--- a/Calculo_Comissoes_08_2025.xlsx
+++ b/Calculo_Comissoes_08_2025.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO17"/>
+  <dimension ref="A1:BO22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,25 +924,25 @@
         <v>0.1</v>
       </c>
       <c r="N2" s="11" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="O2" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="P2" s="12" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Q2" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R2" s="12" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="S2" s="12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="T2" s="12" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="U2" s="13" t="n">
         <v>0.3</v>
@@ -1016,7 +1016,7 @@
         <v>0.25</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.142</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="3">
@@ -1078,25 +1078,25 @@
         <v>0.2</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>0.518</v>
+        <v>0.608</v>
       </c>
       <c r="O3" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="P3" s="12" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Q3" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R3" s="12" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="S3" s="12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="T3" s="12" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="U3" s="13" t="n">
         <v>0.4</v>
@@ -1170,7 +1170,7 @@
         <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.259</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="4">
@@ -1232,25 +1232,25 @@
         <v>0.2</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>0.512</v>
+        <v>0.6320000000000001</v>
       </c>
       <c r="O4" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="P4" s="12" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Q4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R4" s="12" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="S4" s="12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="T4" s="12" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="U4" s="13" t="n">
         <v>0.4</v>
@@ -1324,7 +1324,7 @@
         <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.256</v>
+        <v>0.3160000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1386,7 +1386,7 @@
         <v>0.15</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="O5" s="12" t="inlineStr"/>
       <c r="P5" s="12" t="inlineStr"/>
@@ -1404,19 +1404,19 @@
         <v>0.4</v>
       </c>
       <c r="AB5" s="14" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AC5" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AD5" s="14" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" s="14" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AF5" s="14" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="AG5" s="15" t="n">
         <v>0.6</v>
@@ -1466,7 +1466,7 @@
         <v>0.375</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.15</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="6">
@@ -1528,7 +1528,7 @@
         <v>0.15</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>0.5</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="12" t="inlineStr"/>
@@ -1546,19 +1546,19 @@
         <v>0.6</v>
       </c>
       <c r="AB6" s="14" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AC6" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AD6" s="14" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" s="14" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AF6" s="14" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="AG6" s="15" t="n">
         <v>0.4</v>
@@ -1608,7 +1608,7 @@
         <v>0.375</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1875</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="7">
@@ -1670,25 +1670,25 @@
         <v>0.1</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="O7" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Q7" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="S7" s="12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="T7" s="12" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="U7" s="13" t="n">
         <v>0.3</v>
@@ -1762,7 +1762,7 @@
         <v>0.1</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.034</v>
+        <v>0.04600000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1824,25 +1824,25 @@
         <v>0.2</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Q8" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="S8" s="12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="T8" s="12" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="U8" s="13" t="n">
         <v>0.4</v>
@@ -1916,7 +1916,7 @@
         <v>0.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.05800000000000001</v>
+        <v>0.07600000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1978,25 +1978,25 @@
         <v>0.2</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="O9" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Q9" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="S9" s="12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="T9" s="12" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="U9" s="13" t="n">
         <v>0.4</v>
@@ -2070,7 +2070,7 @@
         <v>0.2</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.09600000000000002</v>
       </c>
     </row>
     <row r="10">
@@ -2132,7 +2132,7 @@
         <v>0.15</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="12" t="inlineStr"/>
@@ -2150,19 +2150,19 @@
         <v>0.4</v>
       </c>
       <c r="AB10" s="14" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AC10" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AD10" s="14" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" s="14" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AF10" s="14" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="AG10" s="15" t="n">
         <v>0.6</v>
@@ -2212,7 +2212,7 @@
         <v>0.15</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.05999999999999999</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="11">
@@ -2274,7 +2274,7 @@
         <v>0.15</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>0.5</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="12" t="inlineStr"/>
@@ -2292,19 +2292,19 @@
         <v>0.6</v>
       </c>
       <c r="AB11" s="14" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AC11" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AD11" s="14" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" s="14" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="14" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="AG11" s="15" t="n">
         <v>0.4</v>
@@ -2354,7 +2354,7 @@
         <v>0.15</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.075</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="12">
@@ -2533,7 +2533,7 @@
         <v>70</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M13" t="n">
         <v>0.1</v>
@@ -2628,10 +2628,10 @@
       <c r="BK13" s="19" t="inlineStr"/>
       <c r="BL13" s="19" t="inlineStr"/>
       <c r="BM13" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.1372</v>
+        <v>0.1715</v>
       </c>
     </row>
     <row r="14">
@@ -2687,7 +2687,7 @@
         <v>70</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M14" t="n">
         <v>0.2</v>
@@ -2782,10 +2782,10 @@
       <c r="BK14" s="19" t="inlineStr"/>
       <c r="BL14" s="19" t="inlineStr"/>
       <c r="BM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.2744</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="15">
@@ -2841,7 +2841,7 @@
         <v>70</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M15" t="n">
         <v>0.2</v>
@@ -2936,10 +2936,10 @@
       <c r="BK15" s="19" t="inlineStr"/>
       <c r="BL15" s="19" t="inlineStr"/>
       <c r="BM15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.3136</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="16">
@@ -2995,7 +2995,7 @@
         <v>70</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M16" t="n">
         <v>0.15</v>
@@ -3078,10 +3078,10 @@
       <c r="BK16" s="19" t="inlineStr"/>
       <c r="BL16" s="19" t="inlineStr"/>
       <c r="BM16" t="n">
-        <v>0.42</v>
+        <v>0.525</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.294</v>
+        <v>0.3675</v>
       </c>
     </row>
     <row r="17">
@@ -3137,7 +3137,7 @@
         <v>70</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M17" t="n">
         <v>0.15</v>
@@ -3216,10 +3216,756 @@
       <c r="BK17" s="19" t="inlineStr"/>
       <c r="BL17" s="19" t="inlineStr"/>
       <c r="BM17" t="n">
-        <v>0.42</v>
+        <v>0.525</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.42</v>
+        <v>0.525</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Paulo Negrão</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Diretor</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>50</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="O18" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P18" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q18" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R18" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U18" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="W18" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="X18" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y18" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z18" s="13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AA18" s="14" t="inlineStr"/>
+      <c r="AB18" s="14" t="inlineStr"/>
+      <c r="AC18" s="14" t="inlineStr"/>
+      <c r="AD18" s="14" t="inlineStr"/>
+      <c r="AE18" s="14" t="inlineStr"/>
+      <c r="AF18" s="14" t="inlineStr"/>
+      <c r="AG18" s="15" t="inlineStr"/>
+      <c r="AH18" s="15" t="inlineStr"/>
+      <c r="AI18" s="15" t="inlineStr"/>
+      <c r="AJ18" s="15" t="inlineStr"/>
+      <c r="AK18" s="15" t="inlineStr"/>
+      <c r="AL18" s="15" t="inlineStr"/>
+      <c r="AM18" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN18" s="16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO18" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP18" s="16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ18" s="16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR18" s="16" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AS18" s="17" t="inlineStr"/>
+      <c r="AT18" s="17" t="inlineStr"/>
+      <c r="AU18" s="17" t="inlineStr"/>
+      <c r="AV18" s="17" t="inlineStr"/>
+      <c r="AW18" s="17" t="inlineStr"/>
+      <c r="AX18" s="17" t="inlineStr"/>
+      <c r="AY18" s="18" t="inlineStr"/>
+      <c r="AZ18" s="18" t="inlineStr"/>
+      <c r="BA18" s="18" t="inlineStr"/>
+      <c r="BB18" s="18" t="inlineStr"/>
+      <c r="BC18" s="18" t="inlineStr"/>
+      <c r="BD18" s="18" t="inlineStr"/>
+      <c r="BE18" s="18" t="inlineStr"/>
+      <c r="BF18" s="19" t="inlineStr"/>
+      <c r="BG18" s="19" t="inlineStr"/>
+      <c r="BH18" s="19" t="inlineStr"/>
+      <c r="BI18" s="19" t="inlineStr"/>
+      <c r="BJ18" s="19" t="inlineStr"/>
+      <c r="BK18" s="19" t="inlineStr"/>
+      <c r="BL18" s="19" t="inlineStr"/>
+      <c r="BM18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Antônio Rosa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Gerente Geral</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>50</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="O19" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P19" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q19" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R19" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U19" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V19" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="W19" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="X19" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y19" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z19" s="13" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AA19" s="14" t="inlineStr"/>
+      <c r="AB19" s="14" t="inlineStr"/>
+      <c r="AC19" s="14" t="inlineStr"/>
+      <c r="AD19" s="14" t="inlineStr"/>
+      <c r="AE19" s="14" t="inlineStr"/>
+      <c r="AF19" s="14" t="inlineStr"/>
+      <c r="AG19" s="15" t="inlineStr"/>
+      <c r="AH19" s="15" t="inlineStr"/>
+      <c r="AI19" s="15" t="inlineStr"/>
+      <c r="AJ19" s="15" t="inlineStr"/>
+      <c r="AK19" s="15" t="inlineStr"/>
+      <c r="AL19" s="15" t="inlineStr"/>
+      <c r="AM19" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN19" s="16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO19" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP19" s="16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ19" s="16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR19" s="16" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AS19" s="17" t="inlineStr"/>
+      <c r="AT19" s="17" t="inlineStr"/>
+      <c r="AU19" s="17" t="inlineStr"/>
+      <c r="AV19" s="17" t="inlineStr"/>
+      <c r="AW19" s="17" t="inlineStr"/>
+      <c r="AX19" s="17" t="inlineStr"/>
+      <c r="AY19" s="18" t="inlineStr"/>
+      <c r="AZ19" s="18" t="inlineStr"/>
+      <c r="BA19" s="18" t="inlineStr"/>
+      <c r="BB19" s="18" t="inlineStr"/>
+      <c r="BC19" s="18" t="inlineStr"/>
+      <c r="BD19" s="18" t="inlineStr"/>
+      <c r="BE19" s="18" t="inlineStr"/>
+      <c r="BF19" s="19" t="inlineStr"/>
+      <c r="BG19" s="19" t="inlineStr"/>
+      <c r="BH19" s="19" t="inlineStr"/>
+      <c r="BI19" s="19" t="inlineStr"/>
+      <c r="BJ19" s="19" t="inlineStr"/>
+      <c r="BK19" s="19" t="inlineStr"/>
+      <c r="BL19" s="19" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0.304</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C007</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Simone</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Coordenador</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>50</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>0.6320000000000001</v>
+      </c>
+      <c r="O20" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P20" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q20" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R20" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U20" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V20" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="W20" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="X20" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y20" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z20" s="13" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AA20" s="14" t="inlineStr"/>
+      <c r="AB20" s="14" t="inlineStr"/>
+      <c r="AC20" s="14" t="inlineStr"/>
+      <c r="AD20" s="14" t="inlineStr"/>
+      <c r="AE20" s="14" t="inlineStr"/>
+      <c r="AF20" s="14" t="inlineStr"/>
+      <c r="AG20" s="15" t="inlineStr"/>
+      <c r="AH20" s="15" t="inlineStr"/>
+      <c r="AI20" s="15" t="inlineStr"/>
+      <c r="AJ20" s="15" t="inlineStr"/>
+      <c r="AK20" s="15" t="inlineStr"/>
+      <c r="AL20" s="15" t="inlineStr"/>
+      <c r="AM20" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN20" s="16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO20" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP20" s="16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ20" s="16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR20" s="16" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="AS20" s="17" t="inlineStr"/>
+      <c r="AT20" s="17" t="inlineStr"/>
+      <c r="AU20" s="17" t="inlineStr"/>
+      <c r="AV20" s="17" t="inlineStr"/>
+      <c r="AW20" s="17" t="inlineStr"/>
+      <c r="AX20" s="17" t="inlineStr"/>
+      <c r="AY20" s="18" t="inlineStr"/>
+      <c r="AZ20" s="18" t="inlineStr"/>
+      <c r="BA20" s="18" t="inlineStr"/>
+      <c r="BB20" s="18" t="inlineStr"/>
+      <c r="BC20" s="18" t="inlineStr"/>
+      <c r="BD20" s="18" t="inlineStr"/>
+      <c r="BE20" s="18" t="inlineStr"/>
+      <c r="BF20" s="19" t="inlineStr"/>
+      <c r="BG20" s="19" t="inlineStr"/>
+      <c r="BH20" s="19" t="inlineStr"/>
+      <c r="BI20" s="19" t="inlineStr"/>
+      <c r="BJ20" s="19" t="inlineStr"/>
+      <c r="BK20" s="19" t="inlineStr"/>
+      <c r="BL20" s="19" t="inlineStr"/>
+      <c r="BM20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0.3160000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C008</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Andrey Andrade</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Consultor Interno</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>50</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O21" s="12" t="inlineStr"/>
+      <c r="P21" s="12" t="inlineStr"/>
+      <c r="Q21" s="12" t="inlineStr"/>
+      <c r="R21" s="12" t="inlineStr"/>
+      <c r="S21" s="12" t="inlineStr"/>
+      <c r="T21" s="12" t="inlineStr"/>
+      <c r="U21" s="13" t="inlineStr"/>
+      <c r="V21" s="13" t="inlineStr"/>
+      <c r="W21" s="13" t="inlineStr"/>
+      <c r="X21" s="13" t="inlineStr"/>
+      <c r="Y21" s="13" t="inlineStr"/>
+      <c r="Z21" s="13" t="inlineStr"/>
+      <c r="AA21" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB21" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC21" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD21" s="14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG21" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH21" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI21" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ21" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK21" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL21" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AM21" s="16" t="inlineStr"/>
+      <c r="AN21" s="16" t="inlineStr"/>
+      <c r="AO21" s="16" t="inlineStr"/>
+      <c r="AP21" s="16" t="inlineStr"/>
+      <c r="AQ21" s="16" t="inlineStr"/>
+      <c r="AR21" s="16" t="inlineStr"/>
+      <c r="AS21" s="17" t="inlineStr"/>
+      <c r="AT21" s="17" t="inlineStr"/>
+      <c r="AU21" s="17" t="inlineStr"/>
+      <c r="AV21" s="17" t="inlineStr"/>
+      <c r="AW21" s="17" t="inlineStr"/>
+      <c r="AX21" s="17" t="inlineStr"/>
+      <c r="AY21" s="18" t="inlineStr"/>
+      <c r="AZ21" s="18" t="inlineStr"/>
+      <c r="BA21" s="18" t="inlineStr"/>
+      <c r="BB21" s="18" t="inlineStr"/>
+      <c r="BC21" s="18" t="inlineStr"/>
+      <c r="BD21" s="18" t="inlineStr"/>
+      <c r="BE21" s="18" t="inlineStr"/>
+      <c r="BF21" s="19" t="inlineStr"/>
+      <c r="BG21" s="19" t="inlineStr"/>
+      <c r="BH21" s="19" t="inlineStr"/>
+      <c r="BI21" s="19" t="inlineStr"/>
+      <c r="BJ21" s="19" t="inlineStr"/>
+      <c r="BK21" s="19" t="inlineStr"/>
+      <c r="BL21" s="19" t="inlineStr"/>
+      <c r="BM21" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C015</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>André Camargo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Consultor Externo</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>50</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="O22" s="12" t="inlineStr"/>
+      <c r="P22" s="12" t="inlineStr"/>
+      <c r="Q22" s="12" t="inlineStr"/>
+      <c r="R22" s="12" t="inlineStr"/>
+      <c r="S22" s="12" t="inlineStr"/>
+      <c r="T22" s="12" t="inlineStr"/>
+      <c r="U22" s="13" t="inlineStr"/>
+      <c r="V22" s="13" t="inlineStr"/>
+      <c r="W22" s="13" t="inlineStr"/>
+      <c r="X22" s="13" t="inlineStr"/>
+      <c r="Y22" s="13" t="inlineStr"/>
+      <c r="Z22" s="13" t="inlineStr"/>
+      <c r="AA22" s="14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB22" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC22" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD22" s="14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG22" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH22" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI22" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ22" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK22" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL22" s="15" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AM22" s="16" t="inlineStr"/>
+      <c r="AN22" s="16" t="inlineStr"/>
+      <c r="AO22" s="16" t="inlineStr"/>
+      <c r="AP22" s="16" t="inlineStr"/>
+      <c r="AQ22" s="16" t="inlineStr"/>
+      <c r="AR22" s="16" t="inlineStr"/>
+      <c r="AS22" s="17" t="inlineStr"/>
+      <c r="AT22" s="17" t="inlineStr"/>
+      <c r="AU22" s="17" t="inlineStr"/>
+      <c r="AV22" s="17" t="inlineStr"/>
+      <c r="AW22" s="17" t="inlineStr"/>
+      <c r="AX22" s="17" t="inlineStr"/>
+      <c r="AY22" s="18" t="inlineStr"/>
+      <c r="AZ22" s="18" t="inlineStr"/>
+      <c r="BA22" s="18" t="inlineStr"/>
+      <c r="BB22" s="18" t="inlineStr"/>
+      <c r="BC22" s="18" t="inlineStr"/>
+      <c r="BD22" s="18" t="inlineStr"/>
+      <c r="BE22" s="18" t="inlineStr"/>
+      <c r="BF22" s="19" t="inlineStr"/>
+      <c r="BG22" s="19" t="inlineStr"/>
+      <c r="BH22" s="19" t="inlineStr"/>
+      <c r="BI22" s="19" t="inlineStr"/>
+      <c r="BJ22" s="19" t="inlineStr"/>
+      <c r="BK22" s="19" t="inlineStr"/>
+      <c r="BL22" s="19" t="inlineStr"/>
+      <c r="BM22" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0.255</v>
       </c>
     </row>
   </sheetData>
@@ -3412,7 +4158,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3132</v>
+        <v>0.5615</v>
       </c>
     </row>
     <row r="3">
@@ -3432,7 +4178,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5914</v>
+        <v>1.027</v>
       </c>
     </row>
     <row r="4">
@@ -3512,7 +4258,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6415999999999999</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="8">
@@ -3532,7 +4278,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="9">
@@ -3572,7 +4318,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.294</v>
+        <v>0.3675</v>
       </c>
     </row>
     <row r="11">
@@ -3672,7 +4418,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.9625000000000001</v>
+        <v>1.312</v>
       </c>
     </row>
     <row r="16">
@@ -3772,7 +4518,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.42</v>
+        <v>0.525</v>
       </c>
     </row>
   </sheetData>
@@ -3786,7 +4532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3836,7 +4582,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': 100002}</t>
+          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': '100002'}</t>
         </is>
       </c>
     </row>
@@ -3853,7 +4599,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': 100002}</t>
+          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': '100002'}</t>
         </is>
       </c>
     </row>
@@ -3899,12 +4645,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rentabilidade não encontrada para chave ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto') (item: PROD400001)</t>
+          <t>Rentabilidade não encontrada para chave ('SSO', 'Detector Fixo', 'XCD', 'Produto') (item: PROD100002)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'chave_busca': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'chave_original': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'item': 'PROD400001', 'processo': 400001}</t>
+          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': 100002}</t>
         </is>
       </c>
     </row>
@@ -3916,12 +4662,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rentabilidade não encontrada para chave ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto') (item: PROD400001)</t>
+          <t>Rentabilidade não encontrada para chave ('SSO', 'Detector Fixo', 'XCD', 'Produto') (item: PROD100002)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'chave_busca': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'chave_original': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'item': 'PROD400001', 'processo': 400001}</t>
+          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': 100002}</t>
         </is>
       </c>
     </row>
@@ -3967,12 +4713,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meta não encontrada para tipo 'faturamento_individual' e chave 'Mateus Machado'.</t>
+          <t>Rentabilidade não encontrada para chave ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto') (item: PROD400001)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'tipo_meta': 'faturamento_individual', 'chave': 'Mateus Machado', 'erro': 'single positional indexer is out-of-bounds'}</t>
+          <t>{'chave_busca': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'chave_original': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'item': 'PROD400001', 'processo': 400001}</t>
         </is>
       </c>
     </row>
@@ -3984,10 +4730,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Rentabilidade não encontrada para chave ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto') (item: PROD400001)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{'chave_busca': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'chave_original': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'item': 'PROD400001', 'processo': 400001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AVISO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Meta não encontrada para tipo 'faturamento_individual' e chave 'Mateus Machado'.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{'tipo_meta': 'faturamento_individual', 'chave': 'Mateus Machado', 'erro': 'single positional indexer is out-of-bounds'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AVISO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Meta não encontrada para tipo 'conversao_individual' e chave 'Mateus Machado'.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>{'tipo_meta': 'conversao_individual', 'chave': 'Mateus Machado', 'erro': 'single positional indexer is out-of-bounds'}</t>
         </is>
@@ -4034,7 +4814,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>﻿Processo, Status Processo, Numero NF, Dt Emissão, Data Aceite, Valor Realizado, Valor Orçado, Consultor Interno, Representante-pedido, Gerente Comercial-Pedido, Negócio, Grupo, Subgrupo, Tipo de Mercadoria, Aplicação Mat./Serv., Cliente, Nome Cliente, Cidade, UF, Código Produto, Descrição Produto, Qtde Atendida, Operação, Fabricante</t>
+          <t>Processo, Status Processo, Numero NF, Dt Emissão, Data Aceite, Valor Realizado, Valor Orçado, Consultor Interno, Representante-pedido, Gerente Comercial-Pedido, Negócio, Grupo, Subgrupo, Tipo de Mercadoria, Aplicação Mat./Serv., Cliente, Nome Cliente, Cidade, UF, Código Produto, Descrição Produto, Qtde Atendida, Operação, Fabricante</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4854,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>﻿Processo, Status Processo, Numero NF, Dt Emissão, Data Aceite, Valor Realizado, Valor Orçado, Consultor Interno, Representante-pedido, Gerente Comercial-Pedido, Negócio, Grupo, Subgrupo, Tipo de Mercadoria, Aplicação Mat./Serv., Cliente, Nome Cliente, Cidade, UF, Código Produto, Descrição Produto, Qtde Atendida, Operação, Fabricante</t>
+          <t>Processo, Status Processo, Numero NF, Dt Emissão, Data Aceite, Valor Realizado, Valor Orçado, Consultor Interno, Representante-pedido, Gerente Comercial-Pedido, Negócio, Grupo, Subgrupo, Tipo de Mercadoria, Aplicação Mat./Serv., Cliente, Nome Cliente, Cidade, UF, Código Produto, Descrição Produto, Qtde Atendida, Operação, Fabricante</t>
         </is>
       </c>
     </row>
@@ -4089,31 +4869,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Processo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Subgrupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Tipo de Mercadoria</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Consultor Interno</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Representante-pedido</t>
         </is>
@@ -4122,25 +4907,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>100002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Detector Portátil</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>MicroClip</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>ANDREY.ANDRADE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
         </is>
@@ -4149,25 +4939,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>100002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Detector Fixo</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>XCD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ANDREY.ANDRADE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
         </is>
@@ -4176,27 +4971,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>400001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Medidor de Vazão Fixo</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>SAMANTA</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>MATEUS BORRO MACHADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>100001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ANDREY.ANDRADE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
         </is>
       </c>
     </row>
@@ -4314,7 +5146,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alessandro Cappi</t>
+          <t>André Caramello</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4324,12 +5156,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PROD100002</t>
+          <t>PROD400001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SSO</t>
+          <t>Hidrologia</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -4337,12 +5169,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ION</t>
+          <t>ISCO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -4391,7 +5223,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>André Caramello</t>
+          <t>Alessandro Cappi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4401,12 +5233,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PROD400001</t>
+          <t>PROD100002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hidrologia</t>
+          <t>SSO</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -4414,12 +5246,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ISCO</t>
+          <t>ION</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -4530,12 +5362,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-11-28T03:27:22.275460</t>
+          <t>2025-11-28T13:23:02.751572</t>
         </is>
       </c>
     </row>

--- a/Calculo_Comissoes_08_2025.xlsx
+++ b/Calculo_Comissoes_08_2025.xlsx
@@ -5367,7 +5367,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-11-28T13:23:02.751572</t>
+          <t>2025-12-01T11:56:26.773272</t>
         </is>
       </c>
     </row>

--- a/Calculo_Comissoes_08_2025.xlsx
+++ b/Calculo_Comissoes_08_2025.xlsx
@@ -5367,7 +5367,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-12-01T11:56:26.773272</t>
+          <t>2025-12-03T16:46:23.690573</t>
         </is>
       </c>
     </row>

--- a/Calculo_Comissoes_08_2025.xlsx
+++ b/Calculo_Comissoes_08_2025.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO22"/>
+  <dimension ref="A1:BO17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,25 +924,25 @@
         <v>0.1</v>
       </c>
       <c r="N2" s="11" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="O2" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="P2" s="12" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="Q2" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R2" s="12" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="S2" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="T2" s="12" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="U2" s="13" t="n">
         <v>0.3</v>
@@ -1016,7 +1016,7 @@
         <v>0.25</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.172</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="3">
@@ -1078,25 +1078,25 @@
         <v>0.2</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>0.608</v>
+        <v>0.518</v>
       </c>
       <c r="O3" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="P3" s="12" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="Q3" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R3" s="12" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="S3" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="T3" s="12" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="U3" s="13" t="n">
         <v>0.4</v>
@@ -1170,7 +1170,7 @@
         <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.304</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="4">
@@ -1232,25 +1232,25 @@
         <v>0.2</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>0.6320000000000001</v>
+        <v>0.512</v>
       </c>
       <c r="O4" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="P4" s="12" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="Q4" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R4" s="12" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="S4" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="T4" s="12" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="U4" s="13" t="n">
         <v>0.4</v>
@@ -1324,7 +1324,7 @@
         <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.3160000000000001</v>
+        <v>0.256</v>
       </c>
     </row>
     <row r="5">
@@ -1386,7 +1386,7 @@
         <v>0.15</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="O5" s="12" t="inlineStr"/>
       <c r="P5" s="12" t="inlineStr"/>
@@ -1404,19 +1404,19 @@
         <v>0.4</v>
       </c>
       <c r="AB5" s="14" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AC5" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AD5" s="14" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AE5" s="14" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AF5" s="14" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="AG5" s="15" t="n">
         <v>0.6</v>
@@ -1466,7 +1466,7 @@
         <v>0.375</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.195</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="6">
@@ -1528,7 +1528,7 @@
         <v>0.15</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="12" t="inlineStr"/>
@@ -1546,19 +1546,19 @@
         <v>0.6</v>
       </c>
       <c r="AB6" s="14" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AC6" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AD6" s="14" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AE6" s="14" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AF6" s="14" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="AG6" s="15" t="n">
         <v>0.4</v>
@@ -1608,7 +1608,7 @@
         <v>0.375</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.255</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="7">
@@ -1670,25 +1670,25 @@
         <v>0.1</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="O7" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="Q7" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="S7" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="T7" s="12" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="U7" s="13" t="n">
         <v>0.3</v>
@@ -1762,7 +1762,7 @@
         <v>0.1</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.04600000000000001</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="8">
@@ -1824,25 +1824,25 @@
         <v>0.2</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="Q8" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="S8" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="T8" s="12" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="U8" s="13" t="n">
         <v>0.4</v>
@@ -1916,7 +1916,7 @@
         <v>0.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.07600000000000001</v>
+        <v>0.05800000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1978,25 +1978,25 @@
         <v>0.2</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="O9" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="Q9" s="12" t="n">
         <v>100</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="S9" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="T9" s="12" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="U9" s="13" t="n">
         <v>0.4</v>
@@ -2070,7 +2070,7 @@
         <v>0.2</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.09600000000000002</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2132,7 +2132,7 @@
         <v>0.15</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="12" t="inlineStr"/>
@@ -2150,19 +2150,19 @@
         <v>0.4</v>
       </c>
       <c r="AB10" s="14" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AC10" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AD10" s="14" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AE10" s="14" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AF10" s="14" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="AG10" s="15" t="n">
         <v>0.6</v>
@@ -2212,7 +2212,7 @@
         <v>0.15</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.078</v>
+        <v>0.05999999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2274,7 +2274,7 @@
         <v>0.15</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="12" t="inlineStr"/>
@@ -2292,19 +2292,19 @@
         <v>0.6</v>
       </c>
       <c r="AB11" s="14" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AC11" s="14" t="n">
         <v>100</v>
       </c>
       <c r="AD11" s="14" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AE11" s="14" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AF11" s="14" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="AG11" s="15" t="n">
         <v>0.4</v>
@@ -2354,7 +2354,7 @@
         <v>0.15</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.102</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="12">
@@ -3222,752 +3222,6 @@
         <v>0.525</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Paulo Negrão</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Diretor</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>100001</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PROD100002</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Produto de Teste - Processo 100002</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SSO</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Detector Portátil</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>MicroClip</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>50</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N18" s="11" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="O18" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P18" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q18" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="R18" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U18" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="V18" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="W18" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="X18" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y18" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z18" s="13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AA18" s="14" t="inlineStr"/>
-      <c r="AB18" s="14" t="inlineStr"/>
-      <c r="AC18" s="14" t="inlineStr"/>
-      <c r="AD18" s="14" t="inlineStr"/>
-      <c r="AE18" s="14" t="inlineStr"/>
-      <c r="AF18" s="14" t="inlineStr"/>
-      <c r="AG18" s="15" t="inlineStr"/>
-      <c r="AH18" s="15" t="inlineStr"/>
-      <c r="AI18" s="15" t="inlineStr"/>
-      <c r="AJ18" s="15" t="inlineStr"/>
-      <c r="AK18" s="15" t="inlineStr"/>
-      <c r="AL18" s="15" t="inlineStr"/>
-      <c r="AM18" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN18" s="16" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AO18" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP18" s="16" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AQ18" s="16" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AR18" s="16" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="AS18" s="17" t="inlineStr"/>
-      <c r="AT18" s="17" t="inlineStr"/>
-      <c r="AU18" s="17" t="inlineStr"/>
-      <c r="AV18" s="17" t="inlineStr"/>
-      <c r="AW18" s="17" t="inlineStr"/>
-      <c r="AX18" s="17" t="inlineStr"/>
-      <c r="AY18" s="18" t="inlineStr"/>
-      <c r="AZ18" s="18" t="inlineStr"/>
-      <c r="BA18" s="18" t="inlineStr"/>
-      <c r="BB18" s="18" t="inlineStr"/>
-      <c r="BC18" s="18" t="inlineStr"/>
-      <c r="BD18" s="18" t="inlineStr"/>
-      <c r="BE18" s="18" t="inlineStr"/>
-      <c r="BF18" s="19" t="inlineStr"/>
-      <c r="BG18" s="19" t="inlineStr"/>
-      <c r="BH18" s="19" t="inlineStr"/>
-      <c r="BI18" s="19" t="inlineStr"/>
-      <c r="BJ18" s="19" t="inlineStr"/>
-      <c r="BK18" s="19" t="inlineStr"/>
-      <c r="BL18" s="19" t="inlineStr"/>
-      <c r="BM18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>0.172</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Antônio Rosa</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Gerente Geral</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>100001</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PROD100002</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Produto de Teste - Processo 100002</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SSO</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Detector Portátil</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>MicroClip</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>50</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N19" s="11" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="O19" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P19" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q19" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="R19" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U19" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V19" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="W19" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="X19" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y19" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z19" s="13" t="n">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="AA19" s="14" t="inlineStr"/>
-      <c r="AB19" s="14" t="inlineStr"/>
-      <c r="AC19" s="14" t="inlineStr"/>
-      <c r="AD19" s="14" t="inlineStr"/>
-      <c r="AE19" s="14" t="inlineStr"/>
-      <c r="AF19" s="14" t="inlineStr"/>
-      <c r="AG19" s="15" t="inlineStr"/>
-      <c r="AH19" s="15" t="inlineStr"/>
-      <c r="AI19" s="15" t="inlineStr"/>
-      <c r="AJ19" s="15" t="inlineStr"/>
-      <c r="AK19" s="15" t="inlineStr"/>
-      <c r="AL19" s="15" t="inlineStr"/>
-      <c r="AM19" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN19" s="16" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AO19" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP19" s="16" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AQ19" s="16" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AR19" s="16" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="AS19" s="17" t="inlineStr"/>
-      <c r="AT19" s="17" t="inlineStr"/>
-      <c r="AU19" s="17" t="inlineStr"/>
-      <c r="AV19" s="17" t="inlineStr"/>
-      <c r="AW19" s="17" t="inlineStr"/>
-      <c r="AX19" s="17" t="inlineStr"/>
-      <c r="AY19" s="18" t="inlineStr"/>
-      <c r="AZ19" s="18" t="inlineStr"/>
-      <c r="BA19" s="18" t="inlineStr"/>
-      <c r="BB19" s="18" t="inlineStr"/>
-      <c r="BC19" s="18" t="inlineStr"/>
-      <c r="BD19" s="18" t="inlineStr"/>
-      <c r="BE19" s="18" t="inlineStr"/>
-      <c r="BF19" s="19" t="inlineStr"/>
-      <c r="BG19" s="19" t="inlineStr"/>
-      <c r="BH19" s="19" t="inlineStr"/>
-      <c r="BI19" s="19" t="inlineStr"/>
-      <c r="BJ19" s="19" t="inlineStr"/>
-      <c r="BK19" s="19" t="inlineStr"/>
-      <c r="BL19" s="19" t="inlineStr"/>
-      <c r="BM19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>0.304</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>C007</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Simone</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Coordenador</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>100001</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>PROD100002</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Produto de Teste - Processo 100002</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SSO</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Detector Portátil</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>MicroClip</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>50</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N20" s="11" t="n">
-        <v>0.6320000000000001</v>
-      </c>
-      <c r="O20" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P20" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q20" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="R20" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U20" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V20" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="W20" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="X20" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y20" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z20" s="13" t="n">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="AA20" s="14" t="inlineStr"/>
-      <c r="AB20" s="14" t="inlineStr"/>
-      <c r="AC20" s="14" t="inlineStr"/>
-      <c r="AD20" s="14" t="inlineStr"/>
-      <c r="AE20" s="14" t="inlineStr"/>
-      <c r="AF20" s="14" t="inlineStr"/>
-      <c r="AG20" s="15" t="inlineStr"/>
-      <c r="AH20" s="15" t="inlineStr"/>
-      <c r="AI20" s="15" t="inlineStr"/>
-      <c r="AJ20" s="15" t="inlineStr"/>
-      <c r="AK20" s="15" t="inlineStr"/>
-      <c r="AL20" s="15" t="inlineStr"/>
-      <c r="AM20" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN20" s="16" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AO20" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP20" s="16" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AQ20" s="16" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AR20" s="16" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="AS20" s="17" t="inlineStr"/>
-      <c r="AT20" s="17" t="inlineStr"/>
-      <c r="AU20" s="17" t="inlineStr"/>
-      <c r="AV20" s="17" t="inlineStr"/>
-      <c r="AW20" s="17" t="inlineStr"/>
-      <c r="AX20" s="17" t="inlineStr"/>
-      <c r="AY20" s="18" t="inlineStr"/>
-      <c r="AZ20" s="18" t="inlineStr"/>
-      <c r="BA20" s="18" t="inlineStr"/>
-      <c r="BB20" s="18" t="inlineStr"/>
-      <c r="BC20" s="18" t="inlineStr"/>
-      <c r="BD20" s="18" t="inlineStr"/>
-      <c r="BE20" s="18" t="inlineStr"/>
-      <c r="BF20" s="19" t="inlineStr"/>
-      <c r="BG20" s="19" t="inlineStr"/>
-      <c r="BH20" s="19" t="inlineStr"/>
-      <c r="BI20" s="19" t="inlineStr"/>
-      <c r="BJ20" s="19" t="inlineStr"/>
-      <c r="BK20" s="19" t="inlineStr"/>
-      <c r="BL20" s="19" t="inlineStr"/>
-      <c r="BM20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>0.3160000000000001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>C008</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Andrey Andrade</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Consultor Interno</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>100001</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>PROD100002</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Produto de Teste - Processo 100002</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SSO</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Detector Portátil</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>MicroClip</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>50</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N21" s="11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="O21" s="12" t="inlineStr"/>
-      <c r="P21" s="12" t="inlineStr"/>
-      <c r="Q21" s="12" t="inlineStr"/>
-      <c r="R21" s="12" t="inlineStr"/>
-      <c r="S21" s="12" t="inlineStr"/>
-      <c r="T21" s="12" t="inlineStr"/>
-      <c r="U21" s="13" t="inlineStr"/>
-      <c r="V21" s="13" t="inlineStr"/>
-      <c r="W21" s="13" t="inlineStr"/>
-      <c r="X21" s="13" t="inlineStr"/>
-      <c r="Y21" s="13" t="inlineStr"/>
-      <c r="Z21" s="13" t="inlineStr"/>
-      <c r="AA21" s="14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AB21" s="14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AC21" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD21" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" s="14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AG21" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH21" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI21" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ21" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK21" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AL21" s="15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AM21" s="16" t="inlineStr"/>
-      <c r="AN21" s="16" t="inlineStr"/>
-      <c r="AO21" s="16" t="inlineStr"/>
-      <c r="AP21" s="16" t="inlineStr"/>
-      <c r="AQ21" s="16" t="inlineStr"/>
-      <c r="AR21" s="16" t="inlineStr"/>
-      <c r="AS21" s="17" t="inlineStr"/>
-      <c r="AT21" s="17" t="inlineStr"/>
-      <c r="AU21" s="17" t="inlineStr"/>
-      <c r="AV21" s="17" t="inlineStr"/>
-      <c r="AW21" s="17" t="inlineStr"/>
-      <c r="AX21" s="17" t="inlineStr"/>
-      <c r="AY21" s="18" t="inlineStr"/>
-      <c r="AZ21" s="18" t="inlineStr"/>
-      <c r="BA21" s="18" t="inlineStr"/>
-      <c r="BB21" s="18" t="inlineStr"/>
-      <c r="BC21" s="18" t="inlineStr"/>
-      <c r="BD21" s="18" t="inlineStr"/>
-      <c r="BE21" s="18" t="inlineStr"/>
-      <c r="BF21" s="19" t="inlineStr"/>
-      <c r="BG21" s="19" t="inlineStr"/>
-      <c r="BH21" s="19" t="inlineStr"/>
-      <c r="BI21" s="19" t="inlineStr"/>
-      <c r="BJ21" s="19" t="inlineStr"/>
-      <c r="BK21" s="19" t="inlineStr"/>
-      <c r="BL21" s="19" t="inlineStr"/>
-      <c r="BM21" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>0.195</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>C015</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>André Camargo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Consultor Externo</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>100001</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PROD100002</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Produto de Teste - Processo 100002</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SSO</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Detector Portátil</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>MicroClip</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>50</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N22" s="11" t="n">
-        <v>0.6799999999999999</v>
-      </c>
-      <c r="O22" s="12" t="inlineStr"/>
-      <c r="P22" s="12" t="inlineStr"/>
-      <c r="Q22" s="12" t="inlineStr"/>
-      <c r="R22" s="12" t="inlineStr"/>
-      <c r="S22" s="12" t="inlineStr"/>
-      <c r="T22" s="12" t="inlineStr"/>
-      <c r="U22" s="13" t="inlineStr"/>
-      <c r="V22" s="13" t="inlineStr"/>
-      <c r="W22" s="13" t="inlineStr"/>
-      <c r="X22" s="13" t="inlineStr"/>
-      <c r="Y22" s="13" t="inlineStr"/>
-      <c r="Z22" s="13" t="inlineStr"/>
-      <c r="AA22" s="14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB22" s="14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AC22" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD22" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" s="14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AG22" s="15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH22" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI22" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ22" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK22" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AL22" s="15" t="n">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="AM22" s="16" t="inlineStr"/>
-      <c r="AN22" s="16" t="inlineStr"/>
-      <c r="AO22" s="16" t="inlineStr"/>
-      <c r="AP22" s="16" t="inlineStr"/>
-      <c r="AQ22" s="16" t="inlineStr"/>
-      <c r="AR22" s="16" t="inlineStr"/>
-      <c r="AS22" s="17" t="inlineStr"/>
-      <c r="AT22" s="17" t="inlineStr"/>
-      <c r="AU22" s="17" t="inlineStr"/>
-      <c r="AV22" s="17" t="inlineStr"/>
-      <c r="AW22" s="17" t="inlineStr"/>
-      <c r="AX22" s="17" t="inlineStr"/>
-      <c r="AY22" s="18" t="inlineStr"/>
-      <c r="AZ22" s="18" t="inlineStr"/>
-      <c r="BA22" s="18" t="inlineStr"/>
-      <c r="BB22" s="18" t="inlineStr"/>
-      <c r="BC22" s="18" t="inlineStr"/>
-      <c r="BD22" s="18" t="inlineStr"/>
-      <c r="BE22" s="18" t="inlineStr"/>
-      <c r="BF22" s="19" t="inlineStr"/>
-      <c r="BG22" s="19" t="inlineStr"/>
-      <c r="BH22" s="19" t="inlineStr"/>
-      <c r="BI22" s="19" t="inlineStr"/>
-      <c r="BJ22" s="19" t="inlineStr"/>
-      <c r="BK22" s="19" t="inlineStr"/>
-      <c r="BL22" s="19" t="inlineStr"/>
-      <c r="BM22" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>0.255</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4158,7 +3412,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5615</v>
+        <v>0.3475</v>
       </c>
     </row>
     <row r="3">
@@ -4178,7 +3432,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.027</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="4">
@@ -4258,7 +3512,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.12</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="8">
@@ -4278,7 +3532,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.468</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="9">
@@ -4418,7 +3672,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.312</v>
+        <v>0.9625000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -4532,7 +3786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4582,7 +3836,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': '100002'}</t>
+          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': 100002}</t>
         </is>
       </c>
     </row>
@@ -4599,7 +3853,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': '100002'}</t>
+          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': 100002}</t>
         </is>
       </c>
     </row>
@@ -4645,12 +3899,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rentabilidade não encontrada para chave ('SSO', 'Detector Fixo', 'XCD', 'Produto') (item: PROD100002)</t>
+          <t>Rentabilidade não encontrada para chave ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto') (item: PROD400001)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': 100002}</t>
+          <t>{'chave_busca': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'chave_original': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'item': 'PROD400001', 'processo': 400001}</t>
         </is>
       </c>
     </row>
@@ -4662,12 +3916,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rentabilidade não encontrada para chave ('SSO', 'Detector Fixo', 'XCD', 'Produto') (item: PROD100002)</t>
+          <t>Rentabilidade não encontrada para chave ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto') (item: PROD400001)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'chave_busca': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'chave_original': ('SSO', 'Detector Fixo', 'XCD', 'Produto'), 'item': 'PROD100002', 'processo': 100002}</t>
+          <t>{'chave_busca': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'chave_original': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'item': 'PROD400001', 'processo': 400001}</t>
         </is>
       </c>
     </row>
@@ -4713,12 +3967,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rentabilidade não encontrada para chave ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto') (item: PROD400001)</t>
+          <t>Meta não encontrada para tipo 'faturamento_individual' e chave 'Mateus Machado'.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'chave_busca': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'chave_original': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'item': 'PROD400001', 'processo': 400001}</t>
+          <t>{'tipo_meta': 'faturamento_individual', 'chave': 'Mateus Machado', 'erro': 'single positional indexer is out-of-bounds'}</t>
         </is>
       </c>
     </row>
@@ -4730,44 +3984,10 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rentabilidade não encontrada para chave ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto') (item: PROD400001)</t>
+          <t>Meta não encontrada para tipo 'conversao_individual' e chave 'Mateus Machado'.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
-        <is>
-          <t>{'chave_busca': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'chave_original': ('Hidrologia', 'Medidor de Vazão Fixo', 'ADP', 'Produto'), 'item': 'PROD400001', 'processo': 400001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AVISO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Meta não encontrada para tipo 'faturamento_individual' e chave 'Mateus Machado'.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'tipo_meta': 'faturamento_individual', 'chave': 'Mateus Machado', 'erro': 'single positional indexer is out-of-bounds'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AVISO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Meta não encontrada para tipo 'conversao_individual' e chave 'Mateus Machado'.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>{'tipo_meta': 'conversao_individual', 'chave': 'Mateus Machado', 'erro': 'single positional indexer is out-of-bounds'}</t>
         </is>
@@ -5146,7 +4366,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>André Caramello</t>
+          <t>Alessandro Cappi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5156,12 +4376,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PROD400001</t>
+          <t>PROD100002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hidrologia</t>
+          <t>SSO</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -5169,12 +4389,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ISCO</t>
+          <t>ION</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -5223,7 +4443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alessandro Cappi</t>
+          <t>André Caramello</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5233,12 +4453,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PROD100002</t>
+          <t>PROD400001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SSO</t>
+          <t>Hidrologia</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -5246,12 +4466,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ION</t>
+          <t>ISCO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -5367,7 +4587,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-12-03T16:46:23.690573</t>
+          <t>2025-12-04T15:08:34.340821</t>
         </is>
       </c>
     </row>

--- a/Calculo_Comissoes_08_2025.xlsx
+++ b/Calculo_Comissoes_08_2025.xlsx
@@ -26,7 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -119,11 +121,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -160,6 +163,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO17"/>
+  <dimension ref="A1:BO22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,257 +598,257 @@
           <t>percentual_elegibilidade_pe</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>fator_correcao_fc</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>peso_fat_linha</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>realizado_fat_linha</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>meta_fat_linha</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>ating_fat_linha</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>ating_cap_fat_linha</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>comp_fc_fat_linha</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>peso_conv_linha</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>realizado_conv_linha</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>meta_conv_linha</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>ating_conv_linha</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>ating_cap_conv_linha</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="Z1" s="5" t="inlineStr">
         <is>
           <t>comp_fc_conv_linha</t>
         </is>
       </c>
-      <c r="AA1" s="5" t="inlineStr">
+      <c r="AA1" s="6" t="inlineStr">
         <is>
           <t>peso_fat_ind</t>
         </is>
       </c>
-      <c r="AB1" s="5" t="inlineStr">
+      <c r="AB1" s="6" t="inlineStr">
         <is>
           <t>realizado_fat_ind</t>
         </is>
       </c>
-      <c r="AC1" s="5" t="inlineStr">
+      <c r="AC1" s="6" t="inlineStr">
         <is>
           <t>meta_fat_ind</t>
         </is>
       </c>
-      <c r="AD1" s="5" t="inlineStr">
+      <c r="AD1" s="6" t="inlineStr">
         <is>
           <t>ating_fat_ind</t>
         </is>
       </c>
-      <c r="AE1" s="5" t="inlineStr">
+      <c r="AE1" s="6" t="inlineStr">
         <is>
           <t>ating_cap_fat_ind</t>
         </is>
       </c>
-      <c r="AF1" s="5" t="inlineStr">
+      <c r="AF1" s="6" t="inlineStr">
         <is>
           <t>comp_fc_fat_ind</t>
         </is>
       </c>
-      <c r="AG1" s="6" t="inlineStr">
+      <c r="AG1" s="7" t="inlineStr">
         <is>
           <t>peso_conv_ind</t>
         </is>
       </c>
-      <c r="AH1" s="6" t="inlineStr">
+      <c r="AH1" s="7" t="inlineStr">
         <is>
           <t>realizado_conv_ind</t>
         </is>
       </c>
-      <c r="AI1" s="6" t="inlineStr">
+      <c r="AI1" s="7" t="inlineStr">
         <is>
           <t>meta_conv_ind</t>
         </is>
       </c>
-      <c r="AJ1" s="6" t="inlineStr">
+      <c r="AJ1" s="7" t="inlineStr">
         <is>
           <t>ating_conv_ind</t>
         </is>
       </c>
-      <c r="AK1" s="6" t="inlineStr">
+      <c r="AK1" s="7" t="inlineStr">
         <is>
           <t>ating_cap_conv_ind</t>
         </is>
       </c>
-      <c r="AL1" s="6" t="inlineStr">
+      <c r="AL1" s="7" t="inlineStr">
         <is>
           <t>comp_fc_conv_ind</t>
         </is>
       </c>
-      <c r="AM1" s="7" t="inlineStr">
+      <c r="AM1" s="8" t="inlineStr">
         <is>
           <t>peso_rentab</t>
         </is>
       </c>
-      <c r="AN1" s="7" t="inlineStr">
+      <c r="AN1" s="8" t="inlineStr">
         <is>
           <t>realizado_rentab</t>
         </is>
       </c>
-      <c r="AO1" s="7" t="inlineStr">
+      <c r="AO1" s="8" t="inlineStr">
         <is>
           <t>meta_rentab</t>
         </is>
       </c>
-      <c r="AP1" s="7" t="inlineStr">
+      <c r="AP1" s="8" t="inlineStr">
         <is>
           <t>ating_rentab</t>
         </is>
       </c>
-      <c r="AQ1" s="7" t="inlineStr">
+      <c r="AQ1" s="8" t="inlineStr">
         <is>
           <t>ating_cap_rentab</t>
         </is>
       </c>
-      <c r="AR1" s="7" t="inlineStr">
+      <c r="AR1" s="8" t="inlineStr">
         <is>
           <t>comp_fc_rentab</t>
         </is>
       </c>
-      <c r="AS1" s="8" t="inlineStr">
+      <c r="AS1" s="9" t="inlineStr">
         <is>
           <t>peso_retencao</t>
         </is>
       </c>
-      <c r="AT1" s="8" t="inlineStr">
+      <c r="AT1" s="9" t="inlineStr">
         <is>
           <t>realizado_retencao</t>
         </is>
       </c>
-      <c r="AU1" s="8" t="inlineStr">
+      <c r="AU1" s="9" t="inlineStr">
         <is>
           <t>meta_retencao</t>
         </is>
       </c>
-      <c r="AV1" s="8" t="inlineStr">
+      <c r="AV1" s="9" t="inlineStr">
         <is>
           <t>ating_retencao</t>
         </is>
       </c>
-      <c r="AW1" s="8" t="inlineStr">
+      <c r="AW1" s="9" t="inlineStr">
         <is>
           <t>ating_cap_retencao</t>
         </is>
       </c>
-      <c r="AX1" s="8" t="inlineStr">
+      <c r="AX1" s="9" t="inlineStr">
         <is>
           <t>comp_fc_retencao</t>
         </is>
       </c>
-      <c r="AY1" s="9" t="inlineStr">
+      <c r="AY1" s="10" t="inlineStr">
         <is>
           <t>peso_forn1</t>
         </is>
       </c>
-      <c r="AZ1" s="9" t="inlineStr">
+      <c r="AZ1" s="10" t="inlineStr">
         <is>
           <t>realizado_forn1</t>
         </is>
       </c>
-      <c r="BA1" s="9" t="inlineStr">
+      <c r="BA1" s="10" t="inlineStr">
         <is>
           <t>meta_forn1</t>
         </is>
       </c>
-      <c r="BB1" s="9" t="inlineStr">
+      <c r="BB1" s="10" t="inlineStr">
         <is>
           <t>ating_forn1</t>
         </is>
       </c>
-      <c r="BC1" s="9" t="inlineStr">
+      <c r="BC1" s="10" t="inlineStr">
         <is>
           <t>ating_cap_forn1</t>
         </is>
       </c>
-      <c r="BD1" s="9" t="inlineStr">
+      <c r="BD1" s="10" t="inlineStr">
         <is>
           <t>comp_fc_forn1</t>
         </is>
       </c>
-      <c r="BE1" s="9" t="inlineStr">
+      <c r="BE1" s="10" t="inlineStr">
         <is>
           <t>moeda_forn1</t>
         </is>
       </c>
-      <c r="BF1" s="10" t="inlineStr">
+      <c r="BF1" s="11" t="inlineStr">
         <is>
           <t>peso_forn2</t>
         </is>
       </c>
-      <c r="BG1" s="10" t="inlineStr">
+      <c r="BG1" s="11" t="inlineStr">
         <is>
           <t>realizado_forn2</t>
         </is>
       </c>
-      <c r="BH1" s="10" t="inlineStr">
+      <c r="BH1" s="11" t="inlineStr">
         <is>
           <t>meta_forn2</t>
         </is>
       </c>
-      <c r="BI1" s="10" t="inlineStr">
+      <c r="BI1" s="11" t="inlineStr">
         <is>
           <t>ating_forn2</t>
         </is>
       </c>
-      <c r="BJ1" s="10" t="inlineStr">
+      <c r="BJ1" s="11" t="inlineStr">
         <is>
           <t>ating_cap_forn2</t>
         </is>
       </c>
-      <c r="BK1" s="10" t="inlineStr">
+      <c r="BK1" s="11" t="inlineStr">
         <is>
           <t>comp_fc_forn2</t>
         </is>
       </c>
-      <c r="BL1" s="10" t="inlineStr">
+      <c r="BL1" s="11" t="inlineStr">
         <is>
           <t>moeda_forn2</t>
         </is>
@@ -923,100 +927,100 @@
       <c r="M2" t="n">
         <v>0.1</v>
       </c>
-      <c r="N2" s="11" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="O2" s="12" t="n">
+      <c r="N2" s="12" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="O2" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="P2" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q2" s="12" t="n">
+      <c r="P2" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q2" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="R2" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S2" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T2" s="12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U2" s="13" t="n">
+      <c r="R2" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U2" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="V2" s="13" t="n">
+      <c r="V2" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="W2" s="13" t="n">
+      <c r="W2" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="X2" s="13" t="n">
+      <c r="X2" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Y2" s="13" t="n">
+      <c r="Y2" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Z2" s="13" t="n">
+      <c r="Z2" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="AA2" s="14" t="inlineStr"/>
-      <c r="AB2" s="14" t="inlineStr"/>
-      <c r="AC2" s="14" t="inlineStr"/>
-      <c r="AD2" s="14" t="inlineStr"/>
-      <c r="AE2" s="14" t="inlineStr"/>
-      <c r="AF2" s="14" t="inlineStr"/>
-      <c r="AG2" s="15" t="inlineStr"/>
-      <c r="AH2" s="15" t="inlineStr"/>
-      <c r="AI2" s="15" t="inlineStr"/>
-      <c r="AJ2" s="15" t="inlineStr"/>
-      <c r="AK2" s="15" t="inlineStr"/>
-      <c r="AL2" s="15" t="inlineStr"/>
-      <c r="AM2" s="16" t="n">
+      <c r="AA2" s="15" t="inlineStr"/>
+      <c r="AB2" s="15" t="inlineStr"/>
+      <c r="AC2" s="15" t="inlineStr"/>
+      <c r="AD2" s="15" t="inlineStr"/>
+      <c r="AE2" s="15" t="inlineStr"/>
+      <c r="AF2" s="15" t="inlineStr"/>
+      <c r="AG2" s="16" t="inlineStr"/>
+      <c r="AH2" s="16" t="inlineStr"/>
+      <c r="AI2" s="16" t="inlineStr"/>
+      <c r="AJ2" s="16" t="inlineStr"/>
+      <c r="AK2" s="16" t="inlineStr"/>
+      <c r="AL2" s="16" t="inlineStr"/>
+      <c r="AM2" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="AN2" s="16" t="n">
+      <c r="AN2" s="17" t="n">
         <v>0.38</v>
       </c>
-      <c r="AO2" s="16" t="n">
+      <c r="AO2" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP2" s="16" t="n">
+      <c r="AP2" s="17" t="n">
         <v>0.76</v>
       </c>
-      <c r="AQ2" s="16" t="n">
+      <c r="AQ2" s="17" t="n">
         <v>0.76</v>
       </c>
-      <c r="AR2" s="16" t="n">
+      <c r="AR2" s="17" t="n">
         <v>0.228</v>
       </c>
-      <c r="AS2" s="17" t="inlineStr"/>
-      <c r="AT2" s="17" t="inlineStr"/>
-      <c r="AU2" s="17" t="inlineStr"/>
-      <c r="AV2" s="17" t="inlineStr"/>
-      <c r="AW2" s="17" t="inlineStr"/>
-      <c r="AX2" s="17" t="inlineStr"/>
-      <c r="AY2" s="18" t="inlineStr"/>
-      <c r="AZ2" s="18" t="inlineStr"/>
-      <c r="BA2" s="18" t="inlineStr"/>
-      <c r="BB2" s="18" t="inlineStr"/>
-      <c r="BC2" s="18" t="inlineStr"/>
-      <c r="BD2" s="18" t="inlineStr"/>
-      <c r="BE2" s="18" t="inlineStr"/>
-      <c r="BF2" s="19" t="inlineStr"/>
-      <c r="BG2" s="19" t="inlineStr"/>
-      <c r="BH2" s="19" t="inlineStr"/>
-      <c r="BI2" s="19" t="inlineStr"/>
-      <c r="BJ2" s="19" t="inlineStr"/>
-      <c r="BK2" s="19" t="inlineStr"/>
-      <c r="BL2" s="19" t="inlineStr"/>
+      <c r="AS2" s="18" t="inlineStr"/>
+      <c r="AT2" s="18" t="inlineStr"/>
+      <c r="AU2" s="18" t="inlineStr"/>
+      <c r="AV2" s="18" t="inlineStr"/>
+      <c r="AW2" s="18" t="inlineStr"/>
+      <c r="AX2" s="18" t="inlineStr"/>
+      <c r="AY2" s="19" t="inlineStr"/>
+      <c r="AZ2" s="19" t="inlineStr"/>
+      <c r="BA2" s="19" t="inlineStr"/>
+      <c r="BB2" s="19" t="inlineStr"/>
+      <c r="BC2" s="19" t="inlineStr"/>
+      <c r="BD2" s="19" t="inlineStr"/>
+      <c r="BE2" s="19" t="inlineStr"/>
+      <c r="BF2" s="20" t="inlineStr"/>
+      <c r="BG2" s="20" t="inlineStr"/>
+      <c r="BH2" s="20" t="inlineStr"/>
+      <c r="BI2" s="20" t="inlineStr"/>
+      <c r="BJ2" s="20" t="inlineStr"/>
+      <c r="BK2" s="20" t="inlineStr"/>
+      <c r="BL2" s="20" t="inlineStr"/>
       <c r="BM2" t="n">
         <v>0.25</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.142</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="3">
@@ -1077,100 +1081,100 @@
       <c r="M3" t="n">
         <v>0.2</v>
       </c>
-      <c r="N3" s="11" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="O3" s="12" t="n">
+      <c r="N3" s="12" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="O3" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="P3" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q3" s="12" t="n">
+      <c r="P3" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q3" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="R3" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S3" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T3" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="U3" s="13" t="n">
+      <c r="R3" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S3" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U3" s="14" t="n">
         <v>0.4</v>
       </c>
-      <c r="V3" s="13" t="n">
+      <c r="V3" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="W3" s="13" t="n">
+      <c r="W3" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="X3" s="13" t="n">
+      <c r="X3" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Y3" s="13" t="n">
+      <c r="Y3" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Z3" s="13" t="n">
+      <c r="Z3" s="14" t="n">
         <v>0.08000000000000002</v>
       </c>
-      <c r="AA3" s="14" t="inlineStr"/>
-      <c r="AB3" s="14" t="inlineStr"/>
-      <c r="AC3" s="14" t="inlineStr"/>
-      <c r="AD3" s="14" t="inlineStr"/>
-      <c r="AE3" s="14" t="inlineStr"/>
-      <c r="AF3" s="14" t="inlineStr"/>
-      <c r="AG3" s="15" t="inlineStr"/>
-      <c r="AH3" s="15" t="inlineStr"/>
-      <c r="AI3" s="15" t="inlineStr"/>
-      <c r="AJ3" s="15" t="inlineStr"/>
-      <c r="AK3" s="15" t="inlineStr"/>
-      <c r="AL3" s="15" t="inlineStr"/>
-      <c r="AM3" s="16" t="n">
+      <c r="AA3" s="15" t="inlineStr"/>
+      <c r="AB3" s="15" t="inlineStr"/>
+      <c r="AC3" s="15" t="inlineStr"/>
+      <c r="AD3" s="15" t="inlineStr"/>
+      <c r="AE3" s="15" t="inlineStr"/>
+      <c r="AF3" s="15" t="inlineStr"/>
+      <c r="AG3" s="16" t="inlineStr"/>
+      <c r="AH3" s="16" t="inlineStr"/>
+      <c r="AI3" s="16" t="inlineStr"/>
+      <c r="AJ3" s="16" t="inlineStr"/>
+      <c r="AK3" s="16" t="inlineStr"/>
+      <c r="AL3" s="16" t="inlineStr"/>
+      <c r="AM3" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="AN3" s="16" t="n">
+      <c r="AN3" s="17" t="n">
         <v>0.38</v>
       </c>
-      <c r="AO3" s="16" t="n">
+      <c r="AO3" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP3" s="16" t="n">
+      <c r="AP3" s="17" t="n">
         <v>0.76</v>
       </c>
-      <c r="AQ3" s="16" t="n">
+      <c r="AQ3" s="17" t="n">
         <v>0.76</v>
       </c>
-      <c r="AR3" s="16" t="n">
+      <c r="AR3" s="17" t="n">
         <v>0.228</v>
       </c>
-      <c r="AS3" s="17" t="inlineStr"/>
-      <c r="AT3" s="17" t="inlineStr"/>
-      <c r="AU3" s="17" t="inlineStr"/>
-      <c r="AV3" s="17" t="inlineStr"/>
-      <c r="AW3" s="17" t="inlineStr"/>
-      <c r="AX3" s="17" t="inlineStr"/>
-      <c r="AY3" s="18" t="inlineStr"/>
-      <c r="AZ3" s="18" t="inlineStr"/>
-      <c r="BA3" s="18" t="inlineStr"/>
-      <c r="BB3" s="18" t="inlineStr"/>
-      <c r="BC3" s="18" t="inlineStr"/>
-      <c r="BD3" s="18" t="inlineStr"/>
-      <c r="BE3" s="18" t="inlineStr"/>
-      <c r="BF3" s="19" t="inlineStr"/>
-      <c r="BG3" s="19" t="inlineStr"/>
-      <c r="BH3" s="19" t="inlineStr"/>
-      <c r="BI3" s="19" t="inlineStr"/>
-      <c r="BJ3" s="19" t="inlineStr"/>
-      <c r="BK3" s="19" t="inlineStr"/>
-      <c r="BL3" s="19" t="inlineStr"/>
+      <c r="AS3" s="18" t="inlineStr"/>
+      <c r="AT3" s="18" t="inlineStr"/>
+      <c r="AU3" s="18" t="inlineStr"/>
+      <c r="AV3" s="18" t="inlineStr"/>
+      <c r="AW3" s="18" t="inlineStr"/>
+      <c r="AX3" s="18" t="inlineStr"/>
+      <c r="AY3" s="19" t="inlineStr"/>
+      <c r="AZ3" s="19" t="inlineStr"/>
+      <c r="BA3" s="19" t="inlineStr"/>
+      <c r="BB3" s="19" t="inlineStr"/>
+      <c r="BC3" s="19" t="inlineStr"/>
+      <c r="BD3" s="19" t="inlineStr"/>
+      <c r="BE3" s="19" t="inlineStr"/>
+      <c r="BF3" s="20" t="inlineStr"/>
+      <c r="BG3" s="20" t="inlineStr"/>
+      <c r="BH3" s="20" t="inlineStr"/>
+      <c r="BI3" s="20" t="inlineStr"/>
+      <c r="BJ3" s="20" t="inlineStr"/>
+      <c r="BK3" s="20" t="inlineStr"/>
+      <c r="BL3" s="20" t="inlineStr"/>
       <c r="BM3" t="n">
         <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.259</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="4">
@@ -1231,100 +1235,100 @@
       <c r="M4" t="n">
         <v>0.2</v>
       </c>
-      <c r="N4" s="11" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="O4" s="12" t="n">
+      <c r="N4" s="12" t="n">
+        <v>0.6320000000000001</v>
+      </c>
+      <c r="O4" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="P4" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="12" t="n">
+      <c r="P4" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q4" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="R4" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S4" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T4" s="12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U4" s="13" t="n">
+      <c r="R4" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="V4" s="13" t="n">
+      <c r="U4" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V4" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="W4" s="13" t="n">
+      <c r="W4" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="X4" s="13" t="n">
+      <c r="X4" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Y4" s="13" t="n">
+      <c r="Y4" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Z4" s="13" t="n">
+      <c r="Z4" s="14" t="n">
         <v>0.08000000000000002</v>
       </c>
-      <c r="AA4" s="14" t="inlineStr"/>
-      <c r="AB4" s="14" t="inlineStr"/>
-      <c r="AC4" s="14" t="inlineStr"/>
-      <c r="AD4" s="14" t="inlineStr"/>
-      <c r="AE4" s="14" t="inlineStr"/>
-      <c r="AF4" s="14" t="inlineStr"/>
-      <c r="AG4" s="15" t="inlineStr"/>
-      <c r="AH4" s="15" t="inlineStr"/>
-      <c r="AI4" s="15" t="inlineStr"/>
-      <c r="AJ4" s="15" t="inlineStr"/>
-      <c r="AK4" s="15" t="inlineStr"/>
-      <c r="AL4" s="15" t="inlineStr"/>
-      <c r="AM4" s="16" t="n">
+      <c r="AA4" s="15" t="inlineStr"/>
+      <c r="AB4" s="15" t="inlineStr"/>
+      <c r="AC4" s="15" t="inlineStr"/>
+      <c r="AD4" s="15" t="inlineStr"/>
+      <c r="AE4" s="15" t="inlineStr"/>
+      <c r="AF4" s="15" t="inlineStr"/>
+      <c r="AG4" s="16" t="inlineStr"/>
+      <c r="AH4" s="16" t="inlineStr"/>
+      <c r="AI4" s="16" t="inlineStr"/>
+      <c r="AJ4" s="16" t="inlineStr"/>
+      <c r="AK4" s="16" t="inlineStr"/>
+      <c r="AL4" s="16" t="inlineStr"/>
+      <c r="AM4" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="AN4" s="16" t="n">
+      <c r="AN4" s="17" t="n">
         <v>0.38</v>
       </c>
-      <c r="AO4" s="16" t="n">
+      <c r="AO4" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP4" s="16" t="n">
+      <c r="AP4" s="17" t="n">
         <v>0.76</v>
       </c>
-      <c r="AQ4" s="16" t="n">
+      <c r="AQ4" s="17" t="n">
         <v>0.76</v>
       </c>
-      <c r="AR4" s="16" t="n">
+      <c r="AR4" s="17" t="n">
         <v>0.152</v>
       </c>
-      <c r="AS4" s="17" t="inlineStr"/>
-      <c r="AT4" s="17" t="inlineStr"/>
-      <c r="AU4" s="17" t="inlineStr"/>
-      <c r="AV4" s="17" t="inlineStr"/>
-      <c r="AW4" s="17" t="inlineStr"/>
-      <c r="AX4" s="17" t="inlineStr"/>
-      <c r="AY4" s="18" t="inlineStr"/>
-      <c r="AZ4" s="18" t="inlineStr"/>
-      <c r="BA4" s="18" t="inlineStr"/>
-      <c r="BB4" s="18" t="inlineStr"/>
-      <c r="BC4" s="18" t="inlineStr"/>
-      <c r="BD4" s="18" t="inlineStr"/>
-      <c r="BE4" s="18" t="inlineStr"/>
-      <c r="BF4" s="19" t="inlineStr"/>
-      <c r="BG4" s="19" t="inlineStr"/>
-      <c r="BH4" s="19" t="inlineStr"/>
-      <c r="BI4" s="19" t="inlineStr"/>
-      <c r="BJ4" s="19" t="inlineStr"/>
-      <c r="BK4" s="19" t="inlineStr"/>
-      <c r="BL4" s="19" t="inlineStr"/>
+      <c r="AS4" s="18" t="inlineStr"/>
+      <c r="AT4" s="18" t="inlineStr"/>
+      <c r="AU4" s="18" t="inlineStr"/>
+      <c r="AV4" s="18" t="inlineStr"/>
+      <c r="AW4" s="18" t="inlineStr"/>
+      <c r="AX4" s="18" t="inlineStr"/>
+      <c r="AY4" s="19" t="inlineStr"/>
+      <c r="AZ4" s="19" t="inlineStr"/>
+      <c r="BA4" s="19" t="inlineStr"/>
+      <c r="BB4" s="19" t="inlineStr"/>
+      <c r="BC4" s="19" t="inlineStr"/>
+      <c r="BD4" s="19" t="inlineStr"/>
+      <c r="BE4" s="19" t="inlineStr"/>
+      <c r="BF4" s="20" t="inlineStr"/>
+      <c r="BG4" s="20" t="inlineStr"/>
+      <c r="BH4" s="20" t="inlineStr"/>
+      <c r="BI4" s="20" t="inlineStr"/>
+      <c r="BJ4" s="20" t="inlineStr"/>
+      <c r="BK4" s="20" t="inlineStr"/>
+      <c r="BL4" s="20" t="inlineStr"/>
       <c r="BM4" t="n">
         <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.256</v>
+        <v>0.3160000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1385,88 +1389,88 @@
       <c r="M5" t="n">
         <v>0.15</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N5" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O5" s="13" t="inlineStr"/>
+      <c r="P5" s="13" t="inlineStr"/>
+      <c r="Q5" s="13" t="inlineStr"/>
+      <c r="R5" s="13" t="inlineStr"/>
+      <c r="S5" s="13" t="inlineStr"/>
+      <c r="T5" s="13" t="inlineStr"/>
+      <c r="U5" s="14" t="inlineStr"/>
+      <c r="V5" s="14" t="inlineStr"/>
+      <c r="W5" s="14" t="inlineStr"/>
+      <c r="X5" s="14" t="inlineStr"/>
+      <c r="Y5" s="14" t="inlineStr"/>
+      <c r="Z5" s="14" t="inlineStr"/>
+      <c r="AA5" s="15" t="n">
         <v>0.4</v>
       </c>
-      <c r="O5" s="12" t="inlineStr"/>
-      <c r="P5" s="12" t="inlineStr"/>
-      <c r="Q5" s="12" t="inlineStr"/>
-      <c r="R5" s="12" t="inlineStr"/>
-      <c r="S5" s="12" t="inlineStr"/>
-      <c r="T5" s="12" t="inlineStr"/>
-      <c r="U5" s="13" t="inlineStr"/>
-      <c r="V5" s="13" t="inlineStr"/>
-      <c r="W5" s="13" t="inlineStr"/>
-      <c r="X5" s="13" t="inlineStr"/>
-      <c r="Y5" s="13" t="inlineStr"/>
-      <c r="Z5" s="13" t="inlineStr"/>
-      <c r="AA5" s="14" t="n">
+      <c r="AB5" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC5" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD5" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="15" t="n">
         <v>0.4</v>
       </c>
-      <c r="AB5" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AC5" s="14" t="n">
+      <c r="AG5" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH5" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI5" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="AD5" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AE5" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AF5" s="14" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AG5" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH5" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI5" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ5" s="15" t="n">
+      <c r="AJ5" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="AK5" s="15" t="n">
+      <c r="AK5" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="AL5" s="15" t="n">
+      <c r="AL5" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="AM5" s="16" t="inlineStr"/>
-      <c r="AN5" s="16" t="inlineStr"/>
-      <c r="AO5" s="16" t="inlineStr"/>
-      <c r="AP5" s="16" t="inlineStr"/>
-      <c r="AQ5" s="16" t="inlineStr"/>
-      <c r="AR5" s="16" t="inlineStr"/>
-      <c r="AS5" s="17" t="inlineStr"/>
-      <c r="AT5" s="17" t="inlineStr"/>
-      <c r="AU5" s="17" t="inlineStr"/>
-      <c r="AV5" s="17" t="inlineStr"/>
-      <c r="AW5" s="17" t="inlineStr"/>
-      <c r="AX5" s="17" t="inlineStr"/>
-      <c r="AY5" s="18" t="inlineStr"/>
-      <c r="AZ5" s="18" t="inlineStr"/>
-      <c r="BA5" s="18" t="inlineStr"/>
-      <c r="BB5" s="18" t="inlineStr"/>
-      <c r="BC5" s="18" t="inlineStr"/>
-      <c r="BD5" s="18" t="inlineStr"/>
-      <c r="BE5" s="18" t="inlineStr"/>
-      <c r="BF5" s="19" t="inlineStr"/>
-      <c r="BG5" s="19" t="inlineStr"/>
-      <c r="BH5" s="19" t="inlineStr"/>
-      <c r="BI5" s="19" t="inlineStr"/>
-      <c r="BJ5" s="19" t="inlineStr"/>
-      <c r="BK5" s="19" t="inlineStr"/>
-      <c r="BL5" s="19" t="inlineStr"/>
+      <c r="AM5" s="17" t="inlineStr"/>
+      <c r="AN5" s="17" t="inlineStr"/>
+      <c r="AO5" s="17" t="inlineStr"/>
+      <c r="AP5" s="17" t="inlineStr"/>
+      <c r="AQ5" s="17" t="inlineStr"/>
+      <c r="AR5" s="17" t="inlineStr"/>
+      <c r="AS5" s="18" t="inlineStr"/>
+      <c r="AT5" s="18" t="inlineStr"/>
+      <c r="AU5" s="18" t="inlineStr"/>
+      <c r="AV5" s="18" t="inlineStr"/>
+      <c r="AW5" s="18" t="inlineStr"/>
+      <c r="AX5" s="18" t="inlineStr"/>
+      <c r="AY5" s="19" t="inlineStr"/>
+      <c r="AZ5" s="19" t="inlineStr"/>
+      <c r="BA5" s="19" t="inlineStr"/>
+      <c r="BB5" s="19" t="inlineStr"/>
+      <c r="BC5" s="19" t="inlineStr"/>
+      <c r="BD5" s="19" t="inlineStr"/>
+      <c r="BE5" s="19" t="inlineStr"/>
+      <c r="BF5" s="20" t="inlineStr"/>
+      <c r="BG5" s="20" t="inlineStr"/>
+      <c r="BH5" s="20" t="inlineStr"/>
+      <c r="BI5" s="20" t="inlineStr"/>
+      <c r="BJ5" s="20" t="inlineStr"/>
+      <c r="BK5" s="20" t="inlineStr"/>
+      <c r="BL5" s="20" t="inlineStr"/>
       <c r="BM5" t="n">
         <v>0.375</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.15</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="6">
@@ -1527,88 +1531,88 @@
       <c r="M6" t="n">
         <v>0.15</v>
       </c>
-      <c r="N6" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O6" s="12" t="inlineStr"/>
-      <c r="P6" s="12" t="inlineStr"/>
-      <c r="Q6" s="12" t="inlineStr"/>
-      <c r="R6" s="12" t="inlineStr"/>
-      <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="12" t="inlineStr"/>
-      <c r="U6" s="13" t="inlineStr"/>
-      <c r="V6" s="13" t="inlineStr"/>
-      <c r="W6" s="13" t="inlineStr"/>
-      <c r="X6" s="13" t="inlineStr"/>
-      <c r="Y6" s="13" t="inlineStr"/>
-      <c r="Z6" s="13" t="inlineStr"/>
-      <c r="AA6" s="14" t="n">
+      <c r="N6" s="12" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="O6" s="13" t="inlineStr"/>
+      <c r="P6" s="13" t="inlineStr"/>
+      <c r="Q6" s="13" t="inlineStr"/>
+      <c r="R6" s="13" t="inlineStr"/>
+      <c r="S6" s="13" t="inlineStr"/>
+      <c r="T6" s="13" t="inlineStr"/>
+      <c r="U6" s="14" t="inlineStr"/>
+      <c r="V6" s="14" t="inlineStr"/>
+      <c r="W6" s="14" t="inlineStr"/>
+      <c r="X6" s="14" t="inlineStr"/>
+      <c r="Y6" s="14" t="inlineStr"/>
+      <c r="Z6" s="14" t="inlineStr"/>
+      <c r="AA6" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB6" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AC6" s="14" t="n">
+      <c r="AB6" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC6" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="AD6" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AE6" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AF6" s="14" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AG6" s="15" t="n">
+      <c r="AD6" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG6" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="AH6" s="15" t="n">
+      <c r="AH6" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="AI6" s="15" t="n">
+      <c r="AI6" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="AJ6" s="15" t="n">
+      <c r="AJ6" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="AK6" s="15" t="n">
+      <c r="AK6" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="AL6" s="15" t="n">
+      <c r="AL6" s="16" t="n">
         <v>0.08000000000000002</v>
       </c>
-      <c r="AM6" s="16" t="inlineStr"/>
-      <c r="AN6" s="16" t="inlineStr"/>
-      <c r="AO6" s="16" t="inlineStr"/>
-      <c r="AP6" s="16" t="inlineStr"/>
-      <c r="AQ6" s="16" t="inlineStr"/>
-      <c r="AR6" s="16" t="inlineStr"/>
-      <c r="AS6" s="17" t="inlineStr"/>
-      <c r="AT6" s="17" t="inlineStr"/>
-      <c r="AU6" s="17" t="inlineStr"/>
-      <c r="AV6" s="17" t="inlineStr"/>
-      <c r="AW6" s="17" t="inlineStr"/>
-      <c r="AX6" s="17" t="inlineStr"/>
-      <c r="AY6" s="18" t="inlineStr"/>
-      <c r="AZ6" s="18" t="inlineStr"/>
-      <c r="BA6" s="18" t="inlineStr"/>
-      <c r="BB6" s="18" t="inlineStr"/>
-      <c r="BC6" s="18" t="inlineStr"/>
-      <c r="BD6" s="18" t="inlineStr"/>
-      <c r="BE6" s="18" t="inlineStr"/>
-      <c r="BF6" s="19" t="inlineStr"/>
-      <c r="BG6" s="19" t="inlineStr"/>
-      <c r="BH6" s="19" t="inlineStr"/>
-      <c r="BI6" s="19" t="inlineStr"/>
-      <c r="BJ6" s="19" t="inlineStr"/>
-      <c r="BK6" s="19" t="inlineStr"/>
-      <c r="BL6" s="19" t="inlineStr"/>
+      <c r="AM6" s="17" t="inlineStr"/>
+      <c r="AN6" s="17" t="inlineStr"/>
+      <c r="AO6" s="17" t="inlineStr"/>
+      <c r="AP6" s="17" t="inlineStr"/>
+      <c r="AQ6" s="17" t="inlineStr"/>
+      <c r="AR6" s="17" t="inlineStr"/>
+      <c r="AS6" s="18" t="inlineStr"/>
+      <c r="AT6" s="18" t="inlineStr"/>
+      <c r="AU6" s="18" t="inlineStr"/>
+      <c r="AV6" s="18" t="inlineStr"/>
+      <c r="AW6" s="18" t="inlineStr"/>
+      <c r="AX6" s="18" t="inlineStr"/>
+      <c r="AY6" s="19" t="inlineStr"/>
+      <c r="AZ6" s="19" t="inlineStr"/>
+      <c r="BA6" s="19" t="inlineStr"/>
+      <c r="BB6" s="19" t="inlineStr"/>
+      <c r="BC6" s="19" t="inlineStr"/>
+      <c r="BD6" s="19" t="inlineStr"/>
+      <c r="BE6" s="19" t="inlineStr"/>
+      <c r="BF6" s="20" t="inlineStr"/>
+      <c r="BG6" s="20" t="inlineStr"/>
+      <c r="BH6" s="20" t="inlineStr"/>
+      <c r="BI6" s="20" t="inlineStr"/>
+      <c r="BJ6" s="20" t="inlineStr"/>
+      <c r="BK6" s="20" t="inlineStr"/>
+      <c r="BL6" s="20" t="inlineStr"/>
       <c r="BM6" t="n">
         <v>0.375</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1875</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="7">
@@ -1669,100 +1673,100 @@
       <c r="M7" t="n">
         <v>0.1</v>
       </c>
-      <c r="N7" s="11" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="O7" s="12" t="n">
+      <c r="N7" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O7" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="P7" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q7" s="12" t="n">
+      <c r="P7" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q7" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="R7" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S7" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T7" s="12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U7" s="13" t="n">
+      <c r="R7" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U7" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="V7" s="13" t="n">
+      <c r="V7" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="W7" s="13" t="n">
+      <c r="W7" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="X7" s="13" t="n">
+      <c r="X7" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Y7" s="13" t="n">
+      <c r="Y7" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Z7" s="13" t="n">
+      <c r="Z7" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="AA7" s="14" t="inlineStr"/>
-      <c r="AB7" s="14" t="inlineStr"/>
-      <c r="AC7" s="14" t="inlineStr"/>
-      <c r="AD7" s="14" t="inlineStr"/>
-      <c r="AE7" s="14" t="inlineStr"/>
-      <c r="AF7" s="14" t="inlineStr"/>
-      <c r="AG7" s="15" t="inlineStr"/>
-      <c r="AH7" s="15" t="inlineStr"/>
-      <c r="AI7" s="15" t="inlineStr"/>
-      <c r="AJ7" s="15" t="inlineStr"/>
-      <c r="AK7" s="15" t="inlineStr"/>
-      <c r="AL7" s="15" t="inlineStr"/>
-      <c r="AM7" s="16" t="n">
+      <c r="AA7" s="15" t="inlineStr"/>
+      <c r="AB7" s="15" t="inlineStr"/>
+      <c r="AC7" s="15" t="inlineStr"/>
+      <c r="AD7" s="15" t="inlineStr"/>
+      <c r="AE7" s="15" t="inlineStr"/>
+      <c r="AF7" s="15" t="inlineStr"/>
+      <c r="AG7" s="16" t="inlineStr"/>
+      <c r="AH7" s="16" t="inlineStr"/>
+      <c r="AI7" s="16" t="inlineStr"/>
+      <c r="AJ7" s="16" t="inlineStr"/>
+      <c r="AK7" s="16" t="inlineStr"/>
+      <c r="AL7" s="16" t="inlineStr"/>
+      <c r="AM7" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="AN7" s="16" t="n">
+      <c r="AN7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AO7" s="16" t="n">
+      <c r="AO7" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP7" s="16" t="n">
+      <c r="AP7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AQ7" s="16" t="n">
+      <c r="AQ7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AR7" s="16" t="n">
+      <c r="AR7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AS7" s="17" t="inlineStr"/>
-      <c r="AT7" s="17" t="inlineStr"/>
-      <c r="AU7" s="17" t="inlineStr"/>
-      <c r="AV7" s="17" t="inlineStr"/>
-      <c r="AW7" s="17" t="inlineStr"/>
-      <c r="AX7" s="17" t="inlineStr"/>
-      <c r="AY7" s="18" t="inlineStr"/>
-      <c r="AZ7" s="18" t="inlineStr"/>
-      <c r="BA7" s="18" t="inlineStr"/>
-      <c r="BB7" s="18" t="inlineStr"/>
-      <c r="BC7" s="18" t="inlineStr"/>
-      <c r="BD7" s="18" t="inlineStr"/>
-      <c r="BE7" s="18" t="inlineStr"/>
-      <c r="BF7" s="19" t="inlineStr"/>
-      <c r="BG7" s="19" t="inlineStr"/>
-      <c r="BH7" s="19" t="inlineStr"/>
-      <c r="BI7" s="19" t="inlineStr"/>
-      <c r="BJ7" s="19" t="inlineStr"/>
-      <c r="BK7" s="19" t="inlineStr"/>
-      <c r="BL7" s="19" t="inlineStr"/>
+      <c r="AS7" s="18" t="inlineStr"/>
+      <c r="AT7" s="18" t="inlineStr"/>
+      <c r="AU7" s="18" t="inlineStr"/>
+      <c r="AV7" s="18" t="inlineStr"/>
+      <c r="AW7" s="18" t="inlineStr"/>
+      <c r="AX7" s="18" t="inlineStr"/>
+      <c r="AY7" s="19" t="inlineStr"/>
+      <c r="AZ7" s="19" t="inlineStr"/>
+      <c r="BA7" s="19" t="inlineStr"/>
+      <c r="BB7" s="19" t="inlineStr"/>
+      <c r="BC7" s="19" t="inlineStr"/>
+      <c r="BD7" s="19" t="inlineStr"/>
+      <c r="BE7" s="19" t="inlineStr"/>
+      <c r="BF7" s="20" t="inlineStr"/>
+      <c r="BG7" s="20" t="inlineStr"/>
+      <c r="BH7" s="20" t="inlineStr"/>
+      <c r="BI7" s="20" t="inlineStr"/>
+      <c r="BJ7" s="20" t="inlineStr"/>
+      <c r="BK7" s="20" t="inlineStr"/>
+      <c r="BL7" s="20" t="inlineStr"/>
       <c r="BM7" t="n">
         <v>0.1</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.034</v>
+        <v>0.04600000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1823,100 +1827,100 @@
       <c r="M8" t="n">
         <v>0.2</v>
       </c>
-      <c r="N8" s="11" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O8" s="12" t="n">
+      <c r="N8" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O8" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="P8" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q8" s="12" t="n">
+      <c r="P8" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q8" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="R8" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S8" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T8" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="U8" s="13" t="n">
+      <c r="R8" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U8" s="14" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="13" t="n">
+      <c r="V8" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="W8" s="13" t="n">
+      <c r="W8" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="X8" s="13" t="n">
+      <c r="X8" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Y8" s="13" t="n">
+      <c r="Y8" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Z8" s="13" t="n">
+      <c r="Z8" s="14" t="n">
         <v>0.08000000000000002</v>
       </c>
-      <c r="AA8" s="14" t="inlineStr"/>
-      <c r="AB8" s="14" t="inlineStr"/>
-      <c r="AC8" s="14" t="inlineStr"/>
-      <c r="AD8" s="14" t="inlineStr"/>
-      <c r="AE8" s="14" t="inlineStr"/>
-      <c r="AF8" s="14" t="inlineStr"/>
-      <c r="AG8" s="15" t="inlineStr"/>
-      <c r="AH8" s="15" t="inlineStr"/>
-      <c r="AI8" s="15" t="inlineStr"/>
-      <c r="AJ8" s="15" t="inlineStr"/>
-      <c r="AK8" s="15" t="inlineStr"/>
-      <c r="AL8" s="15" t="inlineStr"/>
-      <c r="AM8" s="16" t="n">
+      <c r="AA8" s="15" t="inlineStr"/>
+      <c r="AB8" s="15" t="inlineStr"/>
+      <c r="AC8" s="15" t="inlineStr"/>
+      <c r="AD8" s="15" t="inlineStr"/>
+      <c r="AE8" s="15" t="inlineStr"/>
+      <c r="AF8" s="15" t="inlineStr"/>
+      <c r="AG8" s="16" t="inlineStr"/>
+      <c r="AH8" s="16" t="inlineStr"/>
+      <c r="AI8" s="16" t="inlineStr"/>
+      <c r="AJ8" s="16" t="inlineStr"/>
+      <c r="AK8" s="16" t="inlineStr"/>
+      <c r="AL8" s="16" t="inlineStr"/>
+      <c r="AM8" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="AN8" s="16" t="n">
+      <c r="AN8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AO8" s="16" t="n">
+      <c r="AO8" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP8" s="16" t="n">
+      <c r="AP8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AQ8" s="16" t="n">
+      <c r="AQ8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AR8" s="16" t="n">
+      <c r="AR8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AS8" s="17" t="inlineStr"/>
-      <c r="AT8" s="17" t="inlineStr"/>
-      <c r="AU8" s="17" t="inlineStr"/>
-      <c r="AV8" s="17" t="inlineStr"/>
-      <c r="AW8" s="17" t="inlineStr"/>
-      <c r="AX8" s="17" t="inlineStr"/>
-      <c r="AY8" s="18" t="inlineStr"/>
-      <c r="AZ8" s="18" t="inlineStr"/>
-      <c r="BA8" s="18" t="inlineStr"/>
-      <c r="BB8" s="18" t="inlineStr"/>
-      <c r="BC8" s="18" t="inlineStr"/>
-      <c r="BD8" s="18" t="inlineStr"/>
-      <c r="BE8" s="18" t="inlineStr"/>
-      <c r="BF8" s="19" t="inlineStr"/>
-      <c r="BG8" s="19" t="inlineStr"/>
-      <c r="BH8" s="19" t="inlineStr"/>
-      <c r="BI8" s="19" t="inlineStr"/>
-      <c r="BJ8" s="19" t="inlineStr"/>
-      <c r="BK8" s="19" t="inlineStr"/>
-      <c r="BL8" s="19" t="inlineStr"/>
+      <c r="AS8" s="18" t="inlineStr"/>
+      <c r="AT8" s="18" t="inlineStr"/>
+      <c r="AU8" s="18" t="inlineStr"/>
+      <c r="AV8" s="18" t="inlineStr"/>
+      <c r="AW8" s="18" t="inlineStr"/>
+      <c r="AX8" s="18" t="inlineStr"/>
+      <c r="AY8" s="19" t="inlineStr"/>
+      <c r="AZ8" s="19" t="inlineStr"/>
+      <c r="BA8" s="19" t="inlineStr"/>
+      <c r="BB8" s="19" t="inlineStr"/>
+      <c r="BC8" s="19" t="inlineStr"/>
+      <c r="BD8" s="19" t="inlineStr"/>
+      <c r="BE8" s="19" t="inlineStr"/>
+      <c r="BF8" s="20" t="inlineStr"/>
+      <c r="BG8" s="20" t="inlineStr"/>
+      <c r="BH8" s="20" t="inlineStr"/>
+      <c r="BI8" s="20" t="inlineStr"/>
+      <c r="BJ8" s="20" t="inlineStr"/>
+      <c r="BK8" s="20" t="inlineStr"/>
+      <c r="BL8" s="20" t="inlineStr"/>
       <c r="BM8" t="n">
         <v>0.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.05800000000000001</v>
+        <v>0.07600000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1977,100 +1981,100 @@
       <c r="M9" t="n">
         <v>0.2</v>
       </c>
-      <c r="N9" s="11" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O9" s="12" t="n">
+      <c r="N9" s="12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O9" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="P9" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q9" s="12" t="n">
+      <c r="P9" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q9" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="R9" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S9" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T9" s="12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U9" s="13" t="n">
+      <c r="R9" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="V9" s="13" t="n">
+      <c r="U9" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V9" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="W9" s="13" t="n">
+      <c r="W9" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="X9" s="13" t="n">
+      <c r="X9" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Y9" s="13" t="n">
+      <c r="Y9" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="Z9" s="13" t="n">
+      <c r="Z9" s="14" t="n">
         <v>0.08000000000000002</v>
       </c>
-      <c r="AA9" s="14" t="inlineStr"/>
-      <c r="AB9" s="14" t="inlineStr"/>
-      <c r="AC9" s="14" t="inlineStr"/>
-      <c r="AD9" s="14" t="inlineStr"/>
-      <c r="AE9" s="14" t="inlineStr"/>
-      <c r="AF9" s="14" t="inlineStr"/>
-      <c r="AG9" s="15" t="inlineStr"/>
-      <c r="AH9" s="15" t="inlineStr"/>
-      <c r="AI9" s="15" t="inlineStr"/>
-      <c r="AJ9" s="15" t="inlineStr"/>
-      <c r="AK9" s="15" t="inlineStr"/>
-      <c r="AL9" s="15" t="inlineStr"/>
-      <c r="AM9" s="16" t="n">
+      <c r="AA9" s="15" t="inlineStr"/>
+      <c r="AB9" s="15" t="inlineStr"/>
+      <c r="AC9" s="15" t="inlineStr"/>
+      <c r="AD9" s="15" t="inlineStr"/>
+      <c r="AE9" s="15" t="inlineStr"/>
+      <c r="AF9" s="15" t="inlineStr"/>
+      <c r="AG9" s="16" t="inlineStr"/>
+      <c r="AH9" s="16" t="inlineStr"/>
+      <c r="AI9" s="16" t="inlineStr"/>
+      <c r="AJ9" s="16" t="inlineStr"/>
+      <c r="AK9" s="16" t="inlineStr"/>
+      <c r="AL9" s="16" t="inlineStr"/>
+      <c r="AM9" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="AN9" s="16" t="n">
+      <c r="AN9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AO9" s="16" t="n">
+      <c r="AO9" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP9" s="16" t="n">
+      <c r="AP9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AQ9" s="16" t="n">
+      <c r="AQ9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AR9" s="16" t="n">
+      <c r="AR9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AS9" s="17" t="inlineStr"/>
-      <c r="AT9" s="17" t="inlineStr"/>
-      <c r="AU9" s="17" t="inlineStr"/>
-      <c r="AV9" s="17" t="inlineStr"/>
-      <c r="AW9" s="17" t="inlineStr"/>
-      <c r="AX9" s="17" t="inlineStr"/>
-      <c r="AY9" s="18" t="inlineStr"/>
-      <c r="AZ9" s="18" t="inlineStr"/>
-      <c r="BA9" s="18" t="inlineStr"/>
-      <c r="BB9" s="18" t="inlineStr"/>
-      <c r="BC9" s="18" t="inlineStr"/>
-      <c r="BD9" s="18" t="inlineStr"/>
-      <c r="BE9" s="18" t="inlineStr"/>
-      <c r="BF9" s="19" t="inlineStr"/>
-      <c r="BG9" s="19" t="inlineStr"/>
-      <c r="BH9" s="19" t="inlineStr"/>
-      <c r="BI9" s="19" t="inlineStr"/>
-      <c r="BJ9" s="19" t="inlineStr"/>
-      <c r="BK9" s="19" t="inlineStr"/>
-      <c r="BL9" s="19" t="inlineStr"/>
+      <c r="AS9" s="18" t="inlineStr"/>
+      <c r="AT9" s="18" t="inlineStr"/>
+      <c r="AU9" s="18" t="inlineStr"/>
+      <c r="AV9" s="18" t="inlineStr"/>
+      <c r="AW9" s="18" t="inlineStr"/>
+      <c r="AX9" s="18" t="inlineStr"/>
+      <c r="AY9" s="19" t="inlineStr"/>
+      <c r="AZ9" s="19" t="inlineStr"/>
+      <c r="BA9" s="19" t="inlineStr"/>
+      <c r="BB9" s="19" t="inlineStr"/>
+      <c r="BC9" s="19" t="inlineStr"/>
+      <c r="BD9" s="19" t="inlineStr"/>
+      <c r="BE9" s="19" t="inlineStr"/>
+      <c r="BF9" s="20" t="inlineStr"/>
+      <c r="BG9" s="20" t="inlineStr"/>
+      <c r="BH9" s="20" t="inlineStr"/>
+      <c r="BI9" s="20" t="inlineStr"/>
+      <c r="BJ9" s="20" t="inlineStr"/>
+      <c r="BK9" s="20" t="inlineStr"/>
+      <c r="BL9" s="20" t="inlineStr"/>
       <c r="BM9" t="n">
         <v>0.2</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.09600000000000002</v>
       </c>
     </row>
     <row r="10">
@@ -2131,88 +2135,88 @@
       <c r="M10" t="n">
         <v>0.15</v>
       </c>
-      <c r="N10" s="11" t="n">
+      <c r="N10" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O10" s="13" t="inlineStr"/>
+      <c r="P10" s="13" t="inlineStr"/>
+      <c r="Q10" s="13" t="inlineStr"/>
+      <c r="R10" s="13" t="inlineStr"/>
+      <c r="S10" s="13" t="inlineStr"/>
+      <c r="T10" s="13" t="inlineStr"/>
+      <c r="U10" s="14" t="inlineStr"/>
+      <c r="V10" s="14" t="inlineStr"/>
+      <c r="W10" s="14" t="inlineStr"/>
+      <c r="X10" s="14" t="inlineStr"/>
+      <c r="Y10" s="14" t="inlineStr"/>
+      <c r="Z10" s="14" t="inlineStr"/>
+      <c r="AA10" s="15" t="n">
         <v>0.4</v>
       </c>
-      <c r="O10" s="12" t="inlineStr"/>
-      <c r="P10" s="12" t="inlineStr"/>
-      <c r="Q10" s="12" t="inlineStr"/>
-      <c r="R10" s="12" t="inlineStr"/>
-      <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="12" t="inlineStr"/>
-      <c r="U10" s="13" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="W10" s="13" t="inlineStr"/>
-      <c r="X10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
-      <c r="Z10" s="13" t="inlineStr"/>
-      <c r="AA10" s="14" t="n">
+      <c r="AB10" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC10" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD10" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="15" t="n">
         <v>0.4</v>
       </c>
-      <c r="AB10" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AC10" s="14" t="n">
+      <c r="AG10" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH10" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI10" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="AD10" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AE10" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AF10" s="14" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AG10" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH10" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI10" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ10" s="15" t="n">
+      <c r="AJ10" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="AK10" s="15" t="n">
+      <c r="AK10" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="AL10" s="15" t="n">
+      <c r="AL10" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="AM10" s="16" t="inlineStr"/>
-      <c r="AN10" s="16" t="inlineStr"/>
-      <c r="AO10" s="16" t="inlineStr"/>
-      <c r="AP10" s="16" t="inlineStr"/>
-      <c r="AQ10" s="16" t="inlineStr"/>
-      <c r="AR10" s="16" t="inlineStr"/>
-      <c r="AS10" s="17" t="inlineStr"/>
-      <c r="AT10" s="17" t="inlineStr"/>
-      <c r="AU10" s="17" t="inlineStr"/>
-      <c r="AV10" s="17" t="inlineStr"/>
-      <c r="AW10" s="17" t="inlineStr"/>
-      <c r="AX10" s="17" t="inlineStr"/>
-      <c r="AY10" s="18" t="inlineStr"/>
-      <c r="AZ10" s="18" t="inlineStr"/>
-      <c r="BA10" s="18" t="inlineStr"/>
-      <c r="BB10" s="18" t="inlineStr"/>
-      <c r="BC10" s="18" t="inlineStr"/>
-      <c r="BD10" s="18" t="inlineStr"/>
-      <c r="BE10" s="18" t="inlineStr"/>
-      <c r="BF10" s="19" t="inlineStr"/>
-      <c r="BG10" s="19" t="inlineStr"/>
-      <c r="BH10" s="19" t="inlineStr"/>
-      <c r="BI10" s="19" t="inlineStr"/>
-      <c r="BJ10" s="19" t="inlineStr"/>
-      <c r="BK10" s="19" t="inlineStr"/>
-      <c r="BL10" s="19" t="inlineStr"/>
+      <c r="AM10" s="17" t="inlineStr"/>
+      <c r="AN10" s="17" t="inlineStr"/>
+      <c r="AO10" s="17" t="inlineStr"/>
+      <c r="AP10" s="17" t="inlineStr"/>
+      <c r="AQ10" s="17" t="inlineStr"/>
+      <c r="AR10" s="17" t="inlineStr"/>
+      <c r="AS10" s="18" t="inlineStr"/>
+      <c r="AT10" s="18" t="inlineStr"/>
+      <c r="AU10" s="18" t="inlineStr"/>
+      <c r="AV10" s="18" t="inlineStr"/>
+      <c r="AW10" s="18" t="inlineStr"/>
+      <c r="AX10" s="18" t="inlineStr"/>
+      <c r="AY10" s="19" t="inlineStr"/>
+      <c r="AZ10" s="19" t="inlineStr"/>
+      <c r="BA10" s="19" t="inlineStr"/>
+      <c r="BB10" s="19" t="inlineStr"/>
+      <c r="BC10" s="19" t="inlineStr"/>
+      <c r="BD10" s="19" t="inlineStr"/>
+      <c r="BE10" s="19" t="inlineStr"/>
+      <c r="BF10" s="20" t="inlineStr"/>
+      <c r="BG10" s="20" t="inlineStr"/>
+      <c r="BH10" s="20" t="inlineStr"/>
+      <c r="BI10" s="20" t="inlineStr"/>
+      <c r="BJ10" s="20" t="inlineStr"/>
+      <c r="BK10" s="20" t="inlineStr"/>
+      <c r="BL10" s="20" t="inlineStr"/>
       <c r="BM10" t="n">
         <v>0.15</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.05999999999999999</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="11">
@@ -2273,88 +2277,88 @@
       <c r="M11" t="n">
         <v>0.15</v>
       </c>
-      <c r="N11" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O11" s="12" t="inlineStr"/>
-      <c r="P11" s="12" t="inlineStr"/>
-      <c r="Q11" s="12" t="inlineStr"/>
-      <c r="R11" s="12" t="inlineStr"/>
-      <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="12" t="inlineStr"/>
-      <c r="U11" s="13" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="W11" s="13" t="inlineStr"/>
-      <c r="X11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
-      <c r="Z11" s="13" t="inlineStr"/>
-      <c r="AA11" s="14" t="n">
+      <c r="N11" s="12" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="O11" s="13" t="inlineStr"/>
+      <c r="P11" s="13" t="inlineStr"/>
+      <c r="Q11" s="13" t="inlineStr"/>
+      <c r="R11" s="13" t="inlineStr"/>
+      <c r="S11" s="13" t="inlineStr"/>
+      <c r="T11" s="13" t="inlineStr"/>
+      <c r="U11" s="14" t="inlineStr"/>
+      <c r="V11" s="14" t="inlineStr"/>
+      <c r="W11" s="14" t="inlineStr"/>
+      <c r="X11" s="14" t="inlineStr"/>
+      <c r="Y11" s="14" t="inlineStr"/>
+      <c r="Z11" s="14" t="inlineStr"/>
+      <c r="AA11" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB11" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AC11" s="14" t="n">
+      <c r="AB11" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC11" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="AD11" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AE11" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AF11" s="14" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AG11" s="15" t="n">
+      <c r="AD11" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG11" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="AH11" s="15" t="n">
+      <c r="AH11" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="AI11" s="15" t="n">
+      <c r="AI11" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="AJ11" s="15" t="n">
+      <c r="AJ11" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="AK11" s="15" t="n">
+      <c r="AK11" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="AL11" s="15" t="n">
+      <c r="AL11" s="16" t="n">
         <v>0.08000000000000002</v>
       </c>
-      <c r="AM11" s="16" t="inlineStr"/>
-      <c r="AN11" s="16" t="inlineStr"/>
-      <c r="AO11" s="16" t="inlineStr"/>
-      <c r="AP11" s="16" t="inlineStr"/>
-      <c r="AQ11" s="16" t="inlineStr"/>
-      <c r="AR11" s="16" t="inlineStr"/>
-      <c r="AS11" s="17" t="inlineStr"/>
-      <c r="AT11" s="17" t="inlineStr"/>
-      <c r="AU11" s="17" t="inlineStr"/>
-      <c r="AV11" s="17" t="inlineStr"/>
-      <c r="AW11" s="17" t="inlineStr"/>
-      <c r="AX11" s="17" t="inlineStr"/>
-      <c r="AY11" s="18" t="inlineStr"/>
-      <c r="AZ11" s="18" t="inlineStr"/>
-      <c r="BA11" s="18" t="inlineStr"/>
-      <c r="BB11" s="18" t="inlineStr"/>
-      <c r="BC11" s="18" t="inlineStr"/>
-      <c r="BD11" s="18" t="inlineStr"/>
-      <c r="BE11" s="18" t="inlineStr"/>
-      <c r="BF11" s="19" t="inlineStr"/>
-      <c r="BG11" s="19" t="inlineStr"/>
-      <c r="BH11" s="19" t="inlineStr"/>
-      <c r="BI11" s="19" t="inlineStr"/>
-      <c r="BJ11" s="19" t="inlineStr"/>
-      <c r="BK11" s="19" t="inlineStr"/>
-      <c r="BL11" s="19" t="inlineStr"/>
+      <c r="AM11" s="17" t="inlineStr"/>
+      <c r="AN11" s="17" t="inlineStr"/>
+      <c r="AO11" s="17" t="inlineStr"/>
+      <c r="AP11" s="17" t="inlineStr"/>
+      <c r="AQ11" s="17" t="inlineStr"/>
+      <c r="AR11" s="17" t="inlineStr"/>
+      <c r="AS11" s="18" t="inlineStr"/>
+      <c r="AT11" s="18" t="inlineStr"/>
+      <c r="AU11" s="18" t="inlineStr"/>
+      <c r="AV11" s="18" t="inlineStr"/>
+      <c r="AW11" s="18" t="inlineStr"/>
+      <c r="AX11" s="18" t="inlineStr"/>
+      <c r="AY11" s="19" t="inlineStr"/>
+      <c r="AZ11" s="19" t="inlineStr"/>
+      <c r="BA11" s="19" t="inlineStr"/>
+      <c r="BB11" s="19" t="inlineStr"/>
+      <c r="BC11" s="19" t="inlineStr"/>
+      <c r="BD11" s="19" t="inlineStr"/>
+      <c r="BE11" s="19" t="inlineStr"/>
+      <c r="BF11" s="20" t="inlineStr"/>
+      <c r="BG11" s="20" t="inlineStr"/>
+      <c r="BH11" s="20" t="inlineStr"/>
+      <c r="BI11" s="20" t="inlineStr"/>
+      <c r="BJ11" s="20" t="inlineStr"/>
+      <c r="BK11" s="20" t="inlineStr"/>
+      <c r="BL11" s="20" t="inlineStr"/>
       <c r="BM11" t="n">
         <v>0.15</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.075</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="12">
@@ -2415,59 +2419,59 @@
       <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="11" t="n">
+      <c r="N12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" s="12" t="inlineStr"/>
-      <c r="P12" s="12" t="inlineStr"/>
-      <c r="Q12" s="12" t="inlineStr"/>
-      <c r="R12" s="12" t="inlineStr"/>
-      <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="12" t="inlineStr"/>
-      <c r="U12" s="13" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="W12" s="13" t="inlineStr"/>
-      <c r="X12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
-      <c r="Z12" s="13" t="inlineStr"/>
-      <c r="AA12" s="14" t="inlineStr"/>
-      <c r="AB12" s="14" t="inlineStr"/>
-      <c r="AC12" s="14" t="inlineStr"/>
-      <c r="AD12" s="14" t="inlineStr"/>
-      <c r="AE12" s="14" t="inlineStr"/>
-      <c r="AF12" s="14" t="inlineStr"/>
-      <c r="AG12" s="15" t="inlineStr"/>
-      <c r="AH12" s="15" t="inlineStr"/>
-      <c r="AI12" s="15" t="inlineStr"/>
-      <c r="AJ12" s="15" t="inlineStr"/>
-      <c r="AK12" s="15" t="inlineStr"/>
-      <c r="AL12" s="15" t="inlineStr"/>
-      <c r="AM12" s="16" t="inlineStr"/>
-      <c r="AN12" s="16" t="inlineStr"/>
-      <c r="AO12" s="16" t="inlineStr"/>
-      <c r="AP12" s="16" t="inlineStr"/>
-      <c r="AQ12" s="16" t="inlineStr"/>
-      <c r="AR12" s="16" t="inlineStr"/>
-      <c r="AS12" s="17" t="inlineStr"/>
-      <c r="AT12" s="17" t="inlineStr"/>
-      <c r="AU12" s="17" t="inlineStr"/>
-      <c r="AV12" s="17" t="inlineStr"/>
-      <c r="AW12" s="17" t="inlineStr"/>
-      <c r="AX12" s="17" t="inlineStr"/>
-      <c r="AY12" s="18" t="inlineStr"/>
-      <c r="AZ12" s="18" t="inlineStr"/>
-      <c r="BA12" s="18" t="inlineStr"/>
-      <c r="BB12" s="18" t="inlineStr"/>
-      <c r="BC12" s="18" t="inlineStr"/>
-      <c r="BD12" s="18" t="inlineStr"/>
-      <c r="BE12" s="18" t="inlineStr"/>
-      <c r="BF12" s="19" t="inlineStr"/>
-      <c r="BG12" s="19" t="inlineStr"/>
-      <c r="BH12" s="19" t="inlineStr"/>
-      <c r="BI12" s="19" t="inlineStr"/>
-      <c r="BJ12" s="19" t="inlineStr"/>
-      <c r="BK12" s="19" t="inlineStr"/>
-      <c r="BL12" s="19" t="inlineStr"/>
+      <c r="O12" s="13" t="inlineStr"/>
+      <c r="P12" s="13" t="inlineStr"/>
+      <c r="Q12" s="13" t="inlineStr"/>
+      <c r="R12" s="13" t="inlineStr"/>
+      <c r="S12" s="13" t="inlineStr"/>
+      <c r="T12" s="13" t="inlineStr"/>
+      <c r="U12" s="14" t="inlineStr"/>
+      <c r="V12" s="14" t="inlineStr"/>
+      <c r="W12" s="14" t="inlineStr"/>
+      <c r="X12" s="14" t="inlineStr"/>
+      <c r="Y12" s="14" t="inlineStr"/>
+      <c r="Z12" s="14" t="inlineStr"/>
+      <c r="AA12" s="15" t="inlineStr"/>
+      <c r="AB12" s="15" t="inlineStr"/>
+      <c r="AC12" s="15" t="inlineStr"/>
+      <c r="AD12" s="15" t="inlineStr"/>
+      <c r="AE12" s="15" t="inlineStr"/>
+      <c r="AF12" s="15" t="inlineStr"/>
+      <c r="AG12" s="16" t="inlineStr"/>
+      <c r="AH12" s="16" t="inlineStr"/>
+      <c r="AI12" s="16" t="inlineStr"/>
+      <c r="AJ12" s="16" t="inlineStr"/>
+      <c r="AK12" s="16" t="inlineStr"/>
+      <c r="AL12" s="16" t="inlineStr"/>
+      <c r="AM12" s="17" t="inlineStr"/>
+      <c r="AN12" s="17" t="inlineStr"/>
+      <c r="AO12" s="17" t="inlineStr"/>
+      <c r="AP12" s="17" t="inlineStr"/>
+      <c r="AQ12" s="17" t="inlineStr"/>
+      <c r="AR12" s="17" t="inlineStr"/>
+      <c r="AS12" s="18" t="inlineStr"/>
+      <c r="AT12" s="18" t="inlineStr"/>
+      <c r="AU12" s="18" t="inlineStr"/>
+      <c r="AV12" s="18" t="inlineStr"/>
+      <c r="AW12" s="18" t="inlineStr"/>
+      <c r="AX12" s="18" t="inlineStr"/>
+      <c r="AY12" s="19" t="inlineStr"/>
+      <c r="AZ12" s="19" t="inlineStr"/>
+      <c r="BA12" s="19" t="inlineStr"/>
+      <c r="BB12" s="19" t="inlineStr"/>
+      <c r="BC12" s="19" t="inlineStr"/>
+      <c r="BD12" s="19" t="inlineStr"/>
+      <c r="BE12" s="19" t="inlineStr"/>
+      <c r="BF12" s="20" t="inlineStr"/>
+      <c r="BG12" s="20" t="inlineStr"/>
+      <c r="BH12" s="20" t="inlineStr"/>
+      <c r="BI12" s="20" t="inlineStr"/>
+      <c r="BJ12" s="20" t="inlineStr"/>
+      <c r="BK12" s="20" t="inlineStr"/>
+      <c r="BL12" s="20" t="inlineStr"/>
       <c r="BM12" t="n">
         <v>0.7000000000000001</v>
       </c>
@@ -2538,95 +2542,95 @@
       <c r="M13" t="n">
         <v>0.1</v>
       </c>
-      <c r="N13" s="11" t="n">
+      <c r="N13" s="12" t="n">
         <v>0.49</v>
       </c>
-      <c r="O13" s="12" t="n">
+      <c r="O13" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="P13" s="12" t="n">
+      <c r="P13" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="Q13" s="12" t="n">
+      <c r="Q13" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="R13" s="12" t="n">
+      <c r="R13" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="S13" s="12" t="n">
+      <c r="S13" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="T13" s="12" t="n">
+      <c r="T13" s="13" t="n">
         <v>0.28</v>
       </c>
-      <c r="U13" s="13" t="n">
+      <c r="U13" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="V13" s="13" t="n">
+      <c r="V13" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="W13" s="13" t="n">
+      <c r="W13" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="X13" s="13" t="n">
+      <c r="X13" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="Y13" s="13" t="n">
+      <c r="Y13" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="Z13" s="13" t="n">
+      <c r="Z13" s="14" t="n">
         <v>0.21</v>
       </c>
-      <c r="AA13" s="14" t="inlineStr"/>
-      <c r="AB13" s="14" t="inlineStr"/>
-      <c r="AC13" s="14" t="inlineStr"/>
-      <c r="AD13" s="14" t="inlineStr"/>
-      <c r="AE13" s="14" t="inlineStr"/>
-      <c r="AF13" s="14" t="inlineStr"/>
-      <c r="AG13" s="15" t="inlineStr"/>
-      <c r="AH13" s="15" t="inlineStr"/>
-      <c r="AI13" s="15" t="inlineStr"/>
-      <c r="AJ13" s="15" t="inlineStr"/>
-      <c r="AK13" s="15" t="inlineStr"/>
-      <c r="AL13" s="15" t="inlineStr"/>
-      <c r="AM13" s="16" t="n">
+      <c r="AA13" s="15" t="inlineStr"/>
+      <c r="AB13" s="15" t="inlineStr"/>
+      <c r="AC13" s="15" t="inlineStr"/>
+      <c r="AD13" s="15" t="inlineStr"/>
+      <c r="AE13" s="15" t="inlineStr"/>
+      <c r="AF13" s="15" t="inlineStr"/>
+      <c r="AG13" s="16" t="inlineStr"/>
+      <c r="AH13" s="16" t="inlineStr"/>
+      <c r="AI13" s="16" t="inlineStr"/>
+      <c r="AJ13" s="16" t="inlineStr"/>
+      <c r="AK13" s="16" t="inlineStr"/>
+      <c r="AL13" s="16" t="inlineStr"/>
+      <c r="AM13" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="AN13" s="16" t="n">
+      <c r="AN13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AO13" s="16" t="n">
+      <c r="AO13" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP13" s="16" t="n">
+      <c r="AP13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AQ13" s="16" t="n">
+      <c r="AQ13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AR13" s="16" t="n">
+      <c r="AR13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AS13" s="17" t="inlineStr"/>
-      <c r="AT13" s="17" t="inlineStr"/>
-      <c r="AU13" s="17" t="inlineStr"/>
-      <c r="AV13" s="17" t="inlineStr"/>
-      <c r="AW13" s="17" t="inlineStr"/>
-      <c r="AX13" s="17" t="inlineStr"/>
-      <c r="AY13" s="18" t="inlineStr"/>
-      <c r="AZ13" s="18" t="inlineStr"/>
-      <c r="BA13" s="18" t="inlineStr"/>
-      <c r="BB13" s="18" t="inlineStr"/>
-      <c r="BC13" s="18" t="inlineStr"/>
-      <c r="BD13" s="18" t="inlineStr"/>
-      <c r="BE13" s="18" t="inlineStr"/>
-      <c r="BF13" s="19" t="inlineStr"/>
-      <c r="BG13" s="19" t="inlineStr"/>
-      <c r="BH13" s="19" t="inlineStr"/>
-      <c r="BI13" s="19" t="inlineStr"/>
-      <c r="BJ13" s="19" t="inlineStr"/>
-      <c r="BK13" s="19" t="inlineStr"/>
-      <c r="BL13" s="19" t="inlineStr"/>
+      <c r="AS13" s="18" t="inlineStr"/>
+      <c r="AT13" s="18" t="inlineStr"/>
+      <c r="AU13" s="18" t="inlineStr"/>
+      <c r="AV13" s="18" t="inlineStr"/>
+      <c r="AW13" s="18" t="inlineStr"/>
+      <c r="AX13" s="18" t="inlineStr"/>
+      <c r="AY13" s="19" t="inlineStr"/>
+      <c r="AZ13" s="19" t="inlineStr"/>
+      <c r="BA13" s="19" t="inlineStr"/>
+      <c r="BB13" s="19" t="inlineStr"/>
+      <c r="BC13" s="19" t="inlineStr"/>
+      <c r="BD13" s="19" t="inlineStr"/>
+      <c r="BE13" s="19" t="inlineStr"/>
+      <c r="BF13" s="20" t="inlineStr"/>
+      <c r="BG13" s="20" t="inlineStr"/>
+      <c r="BH13" s="20" t="inlineStr"/>
+      <c r="BI13" s="20" t="inlineStr"/>
+      <c r="BJ13" s="20" t="inlineStr"/>
+      <c r="BK13" s="20" t="inlineStr"/>
+      <c r="BL13" s="20" t="inlineStr"/>
       <c r="BM13" t="n">
         <v>0.35</v>
       </c>
@@ -2692,95 +2696,95 @@
       <c r="M14" t="n">
         <v>0.2</v>
       </c>
-      <c r="N14" s="11" t="n">
+      <c r="N14" s="12" t="n">
         <v>0.49</v>
       </c>
-      <c r="O14" s="12" t="n">
+      <c r="O14" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="P14" s="12" t="n">
+      <c r="P14" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="Q14" s="12" t="n">
+      <c r="Q14" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="R14" s="12" t="n">
+      <c r="R14" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="S14" s="12" t="n">
+      <c r="S14" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="T14" s="12" t="n">
+      <c r="T14" s="13" t="n">
         <v>0.21</v>
       </c>
-      <c r="U14" s="13" t="n">
+      <c r="U14" s="14" t="n">
         <v>0.4</v>
       </c>
-      <c r="V14" s="13" t="n">
+      <c r="V14" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="W14" s="13" t="n">
+      <c r="W14" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="X14" s="13" t="n">
+      <c r="X14" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="Y14" s="13" t="n">
+      <c r="Y14" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="Z14" s="13" t="n">
+      <c r="Z14" s="14" t="n">
         <v>0.28</v>
       </c>
-      <c r="AA14" s="14" t="inlineStr"/>
-      <c r="AB14" s="14" t="inlineStr"/>
-      <c r="AC14" s="14" t="inlineStr"/>
-      <c r="AD14" s="14" t="inlineStr"/>
-      <c r="AE14" s="14" t="inlineStr"/>
-      <c r="AF14" s="14" t="inlineStr"/>
-      <c r="AG14" s="15" t="inlineStr"/>
-      <c r="AH14" s="15" t="inlineStr"/>
-      <c r="AI14" s="15" t="inlineStr"/>
-      <c r="AJ14" s="15" t="inlineStr"/>
-      <c r="AK14" s="15" t="inlineStr"/>
-      <c r="AL14" s="15" t="inlineStr"/>
-      <c r="AM14" s="16" t="n">
+      <c r="AA14" s="15" t="inlineStr"/>
+      <c r="AB14" s="15" t="inlineStr"/>
+      <c r="AC14" s="15" t="inlineStr"/>
+      <c r="AD14" s="15" t="inlineStr"/>
+      <c r="AE14" s="15" t="inlineStr"/>
+      <c r="AF14" s="15" t="inlineStr"/>
+      <c r="AG14" s="16" t="inlineStr"/>
+      <c r="AH14" s="16" t="inlineStr"/>
+      <c r="AI14" s="16" t="inlineStr"/>
+      <c r="AJ14" s="16" t="inlineStr"/>
+      <c r="AK14" s="16" t="inlineStr"/>
+      <c r="AL14" s="16" t="inlineStr"/>
+      <c r="AM14" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="AN14" s="16" t="n">
+      <c r="AN14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AO14" s="16" t="n">
+      <c r="AO14" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP14" s="16" t="n">
+      <c r="AP14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AQ14" s="16" t="n">
+      <c r="AQ14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AR14" s="16" t="n">
+      <c r="AR14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AS14" s="17" t="inlineStr"/>
-      <c r="AT14" s="17" t="inlineStr"/>
-      <c r="AU14" s="17" t="inlineStr"/>
-      <c r="AV14" s="17" t="inlineStr"/>
-      <c r="AW14" s="17" t="inlineStr"/>
-      <c r="AX14" s="17" t="inlineStr"/>
-      <c r="AY14" s="18" t="inlineStr"/>
-      <c r="AZ14" s="18" t="inlineStr"/>
-      <c r="BA14" s="18" t="inlineStr"/>
-      <c r="BB14" s="18" t="inlineStr"/>
-      <c r="BC14" s="18" t="inlineStr"/>
-      <c r="BD14" s="18" t="inlineStr"/>
-      <c r="BE14" s="18" t="inlineStr"/>
-      <c r="BF14" s="19" t="inlineStr"/>
-      <c r="BG14" s="19" t="inlineStr"/>
-      <c r="BH14" s="19" t="inlineStr"/>
-      <c r="BI14" s="19" t="inlineStr"/>
-      <c r="BJ14" s="19" t="inlineStr"/>
-      <c r="BK14" s="19" t="inlineStr"/>
-      <c r="BL14" s="19" t="inlineStr"/>
+      <c r="AS14" s="18" t="inlineStr"/>
+      <c r="AT14" s="18" t="inlineStr"/>
+      <c r="AU14" s="18" t="inlineStr"/>
+      <c r="AV14" s="18" t="inlineStr"/>
+      <c r="AW14" s="18" t="inlineStr"/>
+      <c r="AX14" s="18" t="inlineStr"/>
+      <c r="AY14" s="19" t="inlineStr"/>
+      <c r="AZ14" s="19" t="inlineStr"/>
+      <c r="BA14" s="19" t="inlineStr"/>
+      <c r="BB14" s="19" t="inlineStr"/>
+      <c r="BC14" s="19" t="inlineStr"/>
+      <c r="BD14" s="19" t="inlineStr"/>
+      <c r="BE14" s="19" t="inlineStr"/>
+      <c r="BF14" s="20" t="inlineStr"/>
+      <c r="BG14" s="20" t="inlineStr"/>
+      <c r="BH14" s="20" t="inlineStr"/>
+      <c r="BI14" s="20" t="inlineStr"/>
+      <c r="BJ14" s="20" t="inlineStr"/>
+      <c r="BK14" s="20" t="inlineStr"/>
+      <c r="BL14" s="20" t="inlineStr"/>
       <c r="BM14" t="n">
         <v>0.7000000000000001</v>
       </c>
@@ -2846,95 +2850,95 @@
       <c r="M15" t="n">
         <v>0.2</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="N15" s="12" t="n">
         <v>0.5599999999999999</v>
       </c>
-      <c r="O15" s="12" t="n">
+      <c r="O15" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="P15" s="12" t="n">
+      <c r="P15" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="Q15" s="12" t="n">
+      <c r="Q15" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="R15" s="12" t="n">
+      <c r="R15" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="S15" s="12" t="n">
+      <c r="S15" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="T15" s="12" t="n">
+      <c r="T15" s="13" t="n">
         <v>0.28</v>
       </c>
-      <c r="U15" s="13" t="n">
+      <c r="U15" s="14" t="n">
         <v>0.4</v>
       </c>
-      <c r="V15" s="13" t="n">
+      <c r="V15" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="W15" s="13" t="n">
+      <c r="W15" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="X15" s="13" t="n">
+      <c r="X15" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="Y15" s="13" t="n">
+      <c r="Y15" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="Z15" s="13" t="n">
+      <c r="Z15" s="14" t="n">
         <v>0.28</v>
       </c>
-      <c r="AA15" s="14" t="inlineStr"/>
-      <c r="AB15" s="14" t="inlineStr"/>
-      <c r="AC15" s="14" t="inlineStr"/>
-      <c r="AD15" s="14" t="inlineStr"/>
-      <c r="AE15" s="14" t="inlineStr"/>
-      <c r="AF15" s="14" t="inlineStr"/>
-      <c r="AG15" s="15" t="inlineStr"/>
-      <c r="AH15" s="15" t="inlineStr"/>
-      <c r="AI15" s="15" t="inlineStr"/>
-      <c r="AJ15" s="15" t="inlineStr"/>
-      <c r="AK15" s="15" t="inlineStr"/>
-      <c r="AL15" s="15" t="inlineStr"/>
-      <c r="AM15" s="16" t="n">
+      <c r="AA15" s="15" t="inlineStr"/>
+      <c r="AB15" s="15" t="inlineStr"/>
+      <c r="AC15" s="15" t="inlineStr"/>
+      <c r="AD15" s="15" t="inlineStr"/>
+      <c r="AE15" s="15" t="inlineStr"/>
+      <c r="AF15" s="15" t="inlineStr"/>
+      <c r="AG15" s="16" t="inlineStr"/>
+      <c r="AH15" s="16" t="inlineStr"/>
+      <c r="AI15" s="16" t="inlineStr"/>
+      <c r="AJ15" s="16" t="inlineStr"/>
+      <c r="AK15" s="16" t="inlineStr"/>
+      <c r="AL15" s="16" t="inlineStr"/>
+      <c r="AM15" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="AN15" s="16" t="n">
+      <c r="AN15" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AO15" s="16" t="n">
+      <c r="AO15" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP15" s="16" t="n">
+      <c r="AP15" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AQ15" s="16" t="n">
+      <c r="AQ15" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AR15" s="16" t="n">
+      <c r="AR15" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AS15" s="17" t="inlineStr"/>
-      <c r="AT15" s="17" t="inlineStr"/>
-      <c r="AU15" s="17" t="inlineStr"/>
-      <c r="AV15" s="17" t="inlineStr"/>
-      <c r="AW15" s="17" t="inlineStr"/>
-      <c r="AX15" s="17" t="inlineStr"/>
-      <c r="AY15" s="18" t="inlineStr"/>
-      <c r="AZ15" s="18" t="inlineStr"/>
-      <c r="BA15" s="18" t="inlineStr"/>
-      <c r="BB15" s="18" t="inlineStr"/>
-      <c r="BC15" s="18" t="inlineStr"/>
-      <c r="BD15" s="18" t="inlineStr"/>
-      <c r="BE15" s="18" t="inlineStr"/>
-      <c r="BF15" s="19" t="inlineStr"/>
-      <c r="BG15" s="19" t="inlineStr"/>
-      <c r="BH15" s="19" t="inlineStr"/>
-      <c r="BI15" s="19" t="inlineStr"/>
-      <c r="BJ15" s="19" t="inlineStr"/>
-      <c r="BK15" s="19" t="inlineStr"/>
-      <c r="BL15" s="19" t="inlineStr"/>
+      <c r="AS15" s="18" t="inlineStr"/>
+      <c r="AT15" s="18" t="inlineStr"/>
+      <c r="AU15" s="18" t="inlineStr"/>
+      <c r="AV15" s="18" t="inlineStr"/>
+      <c r="AW15" s="18" t="inlineStr"/>
+      <c r="AX15" s="18" t="inlineStr"/>
+      <c r="AY15" s="19" t="inlineStr"/>
+      <c r="AZ15" s="19" t="inlineStr"/>
+      <c r="BA15" s="19" t="inlineStr"/>
+      <c r="BB15" s="19" t="inlineStr"/>
+      <c r="BC15" s="19" t="inlineStr"/>
+      <c r="BD15" s="19" t="inlineStr"/>
+      <c r="BE15" s="19" t="inlineStr"/>
+      <c r="BF15" s="20" t="inlineStr"/>
+      <c r="BG15" s="20" t="inlineStr"/>
+      <c r="BH15" s="20" t="inlineStr"/>
+      <c r="BI15" s="20" t="inlineStr"/>
+      <c r="BJ15" s="20" t="inlineStr"/>
+      <c r="BK15" s="20" t="inlineStr"/>
+      <c r="BL15" s="20" t="inlineStr"/>
       <c r="BM15" t="n">
         <v>0.7000000000000001</v>
       </c>
@@ -3000,83 +3004,83 @@
       <c r="M16" t="n">
         <v>0.15</v>
       </c>
-      <c r="N16" s="11" t="n">
+      <c r="N16" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="O16" s="12" t="inlineStr"/>
-      <c r="P16" s="12" t="inlineStr"/>
-      <c r="Q16" s="12" t="inlineStr"/>
-      <c r="R16" s="12" t="inlineStr"/>
-      <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="12" t="inlineStr"/>
-      <c r="U16" s="13" t="inlineStr"/>
-      <c r="V16" s="13" t="inlineStr"/>
-      <c r="W16" s="13" t="inlineStr"/>
-      <c r="X16" s="13" t="inlineStr"/>
-      <c r="Y16" s="13" t="inlineStr"/>
-      <c r="Z16" s="13" t="inlineStr"/>
-      <c r="AA16" s="14" t="n">
+      <c r="O16" s="13" t="inlineStr"/>
+      <c r="P16" s="13" t="inlineStr"/>
+      <c r="Q16" s="13" t="inlineStr"/>
+      <c r="R16" s="13" t="inlineStr"/>
+      <c r="S16" s="13" t="inlineStr"/>
+      <c r="T16" s="13" t="inlineStr"/>
+      <c r="U16" s="14" t="inlineStr"/>
+      <c r="V16" s="14" t="inlineStr"/>
+      <c r="W16" s="14" t="inlineStr"/>
+      <c r="X16" s="14" t="inlineStr"/>
+      <c r="Y16" s="14" t="inlineStr"/>
+      <c r="Z16" s="14" t="inlineStr"/>
+      <c r="AA16" s="15" t="n">
         <v>0.4</v>
       </c>
-      <c r="AB16" s="14" t="n">
+      <c r="AB16" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="AC16" s="14" t="n">
+      <c r="AC16" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="AD16" s="14" t="n">
+      <c r="AD16" s="15" t="n">
         <v>0.7</v>
       </c>
-      <c r="AE16" s="14" t="n">
+      <c r="AE16" s="15" t="n">
         <v>0.7</v>
       </c>
-      <c r="AF16" s="14" t="n">
+      <c r="AF16" s="15" t="n">
         <v>0.28</v>
       </c>
-      <c r="AG16" s="15" t="n">
+      <c r="AG16" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="AH16" s="15" t="n">
+      <c r="AH16" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="AI16" s="15" t="n">
+      <c r="AI16" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="AJ16" s="15" t="n">
+      <c r="AJ16" s="16" t="n">
         <v>0.7</v>
       </c>
-      <c r="AK16" s="15" t="n">
+      <c r="AK16" s="16" t="n">
         <v>0.7</v>
       </c>
-      <c r="AL16" s="15" t="n">
+      <c r="AL16" s="16" t="n">
         <v>0.42</v>
       </c>
-      <c r="AM16" s="16" t="inlineStr"/>
-      <c r="AN16" s="16" t="inlineStr"/>
-      <c r="AO16" s="16" t="inlineStr"/>
-      <c r="AP16" s="16" t="inlineStr"/>
-      <c r="AQ16" s="16" t="inlineStr"/>
-      <c r="AR16" s="16" t="inlineStr"/>
-      <c r="AS16" s="17" t="inlineStr"/>
-      <c r="AT16" s="17" t="inlineStr"/>
-      <c r="AU16" s="17" t="inlineStr"/>
-      <c r="AV16" s="17" t="inlineStr"/>
-      <c r="AW16" s="17" t="inlineStr"/>
-      <c r="AX16" s="17" t="inlineStr"/>
-      <c r="AY16" s="18" t="inlineStr"/>
-      <c r="AZ16" s="18" t="inlineStr"/>
-      <c r="BA16" s="18" t="inlineStr"/>
-      <c r="BB16" s="18" t="inlineStr"/>
-      <c r="BC16" s="18" t="inlineStr"/>
-      <c r="BD16" s="18" t="inlineStr"/>
-      <c r="BE16" s="18" t="inlineStr"/>
-      <c r="BF16" s="19" t="inlineStr"/>
-      <c r="BG16" s="19" t="inlineStr"/>
-      <c r="BH16" s="19" t="inlineStr"/>
-      <c r="BI16" s="19" t="inlineStr"/>
-      <c r="BJ16" s="19" t="inlineStr"/>
-      <c r="BK16" s="19" t="inlineStr"/>
-      <c r="BL16" s="19" t="inlineStr"/>
+      <c r="AM16" s="17" t="inlineStr"/>
+      <c r="AN16" s="17" t="inlineStr"/>
+      <c r="AO16" s="17" t="inlineStr"/>
+      <c r="AP16" s="17" t="inlineStr"/>
+      <c r="AQ16" s="17" t="inlineStr"/>
+      <c r="AR16" s="17" t="inlineStr"/>
+      <c r="AS16" s="18" t="inlineStr"/>
+      <c r="AT16" s="18" t="inlineStr"/>
+      <c r="AU16" s="18" t="inlineStr"/>
+      <c r="AV16" s="18" t="inlineStr"/>
+      <c r="AW16" s="18" t="inlineStr"/>
+      <c r="AX16" s="18" t="inlineStr"/>
+      <c r="AY16" s="19" t="inlineStr"/>
+      <c r="AZ16" s="19" t="inlineStr"/>
+      <c r="BA16" s="19" t="inlineStr"/>
+      <c r="BB16" s="19" t="inlineStr"/>
+      <c r="BC16" s="19" t="inlineStr"/>
+      <c r="BD16" s="19" t="inlineStr"/>
+      <c r="BE16" s="19" t="inlineStr"/>
+      <c r="BF16" s="20" t="inlineStr"/>
+      <c r="BG16" s="20" t="inlineStr"/>
+      <c r="BH16" s="20" t="inlineStr"/>
+      <c r="BI16" s="20" t="inlineStr"/>
+      <c r="BJ16" s="20" t="inlineStr"/>
+      <c r="BK16" s="20" t="inlineStr"/>
+      <c r="BL16" s="20" t="inlineStr"/>
       <c r="BM16" t="n">
         <v>0.525</v>
       </c>
@@ -3142,84 +3146,830 @@
       <c r="M17" t="n">
         <v>0.15</v>
       </c>
-      <c r="N17" s="11" t="n">
+      <c r="N17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="O17" s="12" t="inlineStr"/>
-      <c r="P17" s="12" t="inlineStr"/>
-      <c r="Q17" s="12" t="inlineStr"/>
-      <c r="R17" s="12" t="inlineStr"/>
-      <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="12" t="inlineStr"/>
-      <c r="U17" s="13" t="inlineStr"/>
-      <c r="V17" s="13" t="inlineStr"/>
-      <c r="W17" s="13" t="inlineStr"/>
-      <c r="X17" s="13" t="inlineStr"/>
-      <c r="Y17" s="13" t="inlineStr"/>
-      <c r="Z17" s="13" t="inlineStr"/>
-      <c r="AA17" s="14" t="n">
+      <c r="O17" s="13" t="inlineStr"/>
+      <c r="P17" s="13" t="inlineStr"/>
+      <c r="Q17" s="13" t="inlineStr"/>
+      <c r="R17" s="13" t="inlineStr"/>
+      <c r="S17" s="13" t="inlineStr"/>
+      <c r="T17" s="13" t="inlineStr"/>
+      <c r="U17" s="14" t="inlineStr"/>
+      <c r="V17" s="14" t="inlineStr"/>
+      <c r="W17" s="14" t="inlineStr"/>
+      <c r="X17" s="14" t="inlineStr"/>
+      <c r="Y17" s="14" t="inlineStr"/>
+      <c r="Z17" s="14" t="inlineStr"/>
+      <c r="AA17" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB17" s="14" t="n">
+      <c r="AB17" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="AC17" s="14" t="inlineStr"/>
-      <c r="AD17" s="14" t="n">
+      <c r="AC17" s="15" t="inlineStr"/>
+      <c r="AD17" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AE17" s="14" t="n">
+      <c r="AE17" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AF17" s="14" t="n">
+      <c r="AF17" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="AG17" s="15" t="n">
+      <c r="AG17" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="AH17" s="15" t="n">
+      <c r="AH17" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="AI17" s="15" t="inlineStr"/>
-      <c r="AJ17" s="15" t="n">
+      <c r="AI17" s="16" t="inlineStr"/>
+      <c r="AJ17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="AK17" s="15" t="n">
+      <c r="AK17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="AL17" s="15" t="n">
+      <c r="AL17" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="AM17" s="16" t="inlineStr"/>
-      <c r="AN17" s="16" t="inlineStr"/>
-      <c r="AO17" s="16" t="inlineStr"/>
-      <c r="AP17" s="16" t="inlineStr"/>
-      <c r="AQ17" s="16" t="inlineStr"/>
-      <c r="AR17" s="16" t="inlineStr"/>
-      <c r="AS17" s="17" t="inlineStr"/>
-      <c r="AT17" s="17" t="inlineStr"/>
-      <c r="AU17" s="17" t="inlineStr"/>
-      <c r="AV17" s="17" t="inlineStr"/>
-      <c r="AW17" s="17" t="inlineStr"/>
-      <c r="AX17" s="17" t="inlineStr"/>
-      <c r="AY17" s="18" t="inlineStr"/>
-      <c r="AZ17" s="18" t="inlineStr"/>
-      <c r="BA17" s="18" t="inlineStr"/>
-      <c r="BB17" s="18" t="inlineStr"/>
-      <c r="BC17" s="18" t="inlineStr"/>
-      <c r="BD17" s="18" t="inlineStr"/>
-      <c r="BE17" s="18" t="inlineStr"/>
-      <c r="BF17" s="19" t="inlineStr"/>
-      <c r="BG17" s="19" t="inlineStr"/>
-      <c r="BH17" s="19" t="inlineStr"/>
-      <c r="BI17" s="19" t="inlineStr"/>
-      <c r="BJ17" s="19" t="inlineStr"/>
-      <c r="BK17" s="19" t="inlineStr"/>
-      <c r="BL17" s="19" t="inlineStr"/>
+      <c r="AM17" s="17" t="inlineStr"/>
+      <c r="AN17" s="17" t="inlineStr"/>
+      <c r="AO17" s="17" t="inlineStr"/>
+      <c r="AP17" s="17" t="inlineStr"/>
+      <c r="AQ17" s="17" t="inlineStr"/>
+      <c r="AR17" s="17" t="inlineStr"/>
+      <c r="AS17" s="18" t="inlineStr"/>
+      <c r="AT17" s="18" t="inlineStr"/>
+      <c r="AU17" s="18" t="inlineStr"/>
+      <c r="AV17" s="18" t="inlineStr"/>
+      <c r="AW17" s="18" t="inlineStr"/>
+      <c r="AX17" s="18" t="inlineStr"/>
+      <c r="AY17" s="19" t="inlineStr"/>
+      <c r="AZ17" s="19" t="inlineStr"/>
+      <c r="BA17" s="19" t="inlineStr"/>
+      <c r="BB17" s="19" t="inlineStr"/>
+      <c r="BC17" s="19" t="inlineStr"/>
+      <c r="BD17" s="19" t="inlineStr"/>
+      <c r="BE17" s="19" t="inlineStr"/>
+      <c r="BF17" s="20" t="inlineStr"/>
+      <c r="BG17" s="20" t="inlineStr"/>
+      <c r="BH17" s="20" t="inlineStr"/>
+      <c r="BI17" s="20" t="inlineStr"/>
+      <c r="BJ17" s="20" t="inlineStr"/>
+      <c r="BK17" s="20" t="inlineStr"/>
+      <c r="BL17" s="20" t="inlineStr"/>
       <c r="BM17" t="n">
         <v>0.525</v>
       </c>
       <c r="BN17" t="n">
         <v>0.525</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Paulo Negrão</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Diretor</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>50</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N18" s="12" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P18" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q18" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="R18" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U18" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V18" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="W18" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="X18" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y18" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z18" s="14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AA18" s="15" t="inlineStr"/>
+      <c r="AB18" s="15" t="inlineStr"/>
+      <c r="AC18" s="15" t="inlineStr"/>
+      <c r="AD18" s="15" t="inlineStr"/>
+      <c r="AE18" s="15" t="inlineStr"/>
+      <c r="AF18" s="15" t="inlineStr"/>
+      <c r="AG18" s="16" t="inlineStr"/>
+      <c r="AH18" s="16" t="inlineStr"/>
+      <c r="AI18" s="16" t="inlineStr"/>
+      <c r="AJ18" s="16" t="inlineStr"/>
+      <c r="AK18" s="16" t="inlineStr"/>
+      <c r="AL18" s="16" t="inlineStr"/>
+      <c r="AM18" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN18" s="17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO18" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP18" s="17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ18" s="17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR18" s="17" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AS18" s="18" t="inlineStr"/>
+      <c r="AT18" s="18" t="inlineStr"/>
+      <c r="AU18" s="18" t="inlineStr"/>
+      <c r="AV18" s="18" t="inlineStr"/>
+      <c r="AW18" s="18" t="inlineStr"/>
+      <c r="AX18" s="18" t="inlineStr"/>
+      <c r="AY18" s="19" t="inlineStr"/>
+      <c r="AZ18" s="19" t="inlineStr"/>
+      <c r="BA18" s="19" t="inlineStr"/>
+      <c r="BB18" s="19" t="inlineStr"/>
+      <c r="BC18" s="19" t="inlineStr"/>
+      <c r="BD18" s="19" t="inlineStr"/>
+      <c r="BE18" s="19" t="inlineStr"/>
+      <c r="BF18" s="20" t="inlineStr"/>
+      <c r="BG18" s="20" t="inlineStr"/>
+      <c r="BH18" s="20" t="inlineStr"/>
+      <c r="BI18" s="20" t="inlineStr"/>
+      <c r="BJ18" s="20" t="inlineStr"/>
+      <c r="BK18" s="20" t="inlineStr"/>
+      <c r="BL18" s="20" t="inlineStr"/>
+      <c r="BM18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Antônio Rosa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Gerente Geral</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>50</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N19" s="12" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P19" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q19" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="R19" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U19" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V19" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="W19" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y19" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z19" s="14" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AA19" s="15" t="inlineStr"/>
+      <c r="AB19" s="15" t="inlineStr"/>
+      <c r="AC19" s="15" t="inlineStr"/>
+      <c r="AD19" s="15" t="inlineStr"/>
+      <c r="AE19" s="15" t="inlineStr"/>
+      <c r="AF19" s="15" t="inlineStr"/>
+      <c r="AG19" s="16" t="inlineStr"/>
+      <c r="AH19" s="16" t="inlineStr"/>
+      <c r="AI19" s="16" t="inlineStr"/>
+      <c r="AJ19" s="16" t="inlineStr"/>
+      <c r="AK19" s="16" t="inlineStr"/>
+      <c r="AL19" s="16" t="inlineStr"/>
+      <c r="AM19" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN19" s="17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO19" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP19" s="17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ19" s="17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR19" s="17" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AS19" s="18" t="inlineStr"/>
+      <c r="AT19" s="18" t="inlineStr"/>
+      <c r="AU19" s="18" t="inlineStr"/>
+      <c r="AV19" s="18" t="inlineStr"/>
+      <c r="AW19" s="18" t="inlineStr"/>
+      <c r="AX19" s="18" t="inlineStr"/>
+      <c r="AY19" s="19" t="inlineStr"/>
+      <c r="AZ19" s="19" t="inlineStr"/>
+      <c r="BA19" s="19" t="inlineStr"/>
+      <c r="BB19" s="19" t="inlineStr"/>
+      <c r="BC19" s="19" t="inlineStr"/>
+      <c r="BD19" s="19" t="inlineStr"/>
+      <c r="BE19" s="19" t="inlineStr"/>
+      <c r="BF19" s="20" t="inlineStr"/>
+      <c r="BG19" s="20" t="inlineStr"/>
+      <c r="BH19" s="20" t="inlineStr"/>
+      <c r="BI19" s="20" t="inlineStr"/>
+      <c r="BJ19" s="20" t="inlineStr"/>
+      <c r="BK19" s="20" t="inlineStr"/>
+      <c r="BL19" s="20" t="inlineStr"/>
+      <c r="BM19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0.304</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C007</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Simone</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Coordenador</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>50</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N20" s="12" t="n">
+        <v>0.6320000000000001</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P20" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="R20" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U20" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V20" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="W20" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="X20" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y20" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z20" s="14" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AA20" s="15" t="inlineStr"/>
+      <c r="AB20" s="15" t="inlineStr"/>
+      <c r="AC20" s="15" t="inlineStr"/>
+      <c r="AD20" s="15" t="inlineStr"/>
+      <c r="AE20" s="15" t="inlineStr"/>
+      <c r="AF20" s="15" t="inlineStr"/>
+      <c r="AG20" s="16" t="inlineStr"/>
+      <c r="AH20" s="16" t="inlineStr"/>
+      <c r="AI20" s="16" t="inlineStr"/>
+      <c r="AJ20" s="16" t="inlineStr"/>
+      <c r="AK20" s="16" t="inlineStr"/>
+      <c r="AL20" s="16" t="inlineStr"/>
+      <c r="AM20" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN20" s="17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO20" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP20" s="17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ20" s="17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR20" s="17" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="AS20" s="18" t="inlineStr"/>
+      <c r="AT20" s="18" t="inlineStr"/>
+      <c r="AU20" s="18" t="inlineStr"/>
+      <c r="AV20" s="18" t="inlineStr"/>
+      <c r="AW20" s="18" t="inlineStr"/>
+      <c r="AX20" s="18" t="inlineStr"/>
+      <c r="AY20" s="19" t="inlineStr"/>
+      <c r="AZ20" s="19" t="inlineStr"/>
+      <c r="BA20" s="19" t="inlineStr"/>
+      <c r="BB20" s="19" t="inlineStr"/>
+      <c r="BC20" s="19" t="inlineStr"/>
+      <c r="BD20" s="19" t="inlineStr"/>
+      <c r="BE20" s="19" t="inlineStr"/>
+      <c r="BF20" s="20" t="inlineStr"/>
+      <c r="BG20" s="20" t="inlineStr"/>
+      <c r="BH20" s="20" t="inlineStr"/>
+      <c r="BI20" s="20" t="inlineStr"/>
+      <c r="BJ20" s="20" t="inlineStr"/>
+      <c r="BK20" s="20" t="inlineStr"/>
+      <c r="BL20" s="20" t="inlineStr"/>
+      <c r="BM20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0.3160000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C008</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Andrey Andrade</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Consultor Interno</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>50</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N21" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O21" s="13" t="inlineStr"/>
+      <c r="P21" s="13" t="inlineStr"/>
+      <c r="Q21" s="13" t="inlineStr"/>
+      <c r="R21" s="13" t="inlineStr"/>
+      <c r="S21" s="13" t="inlineStr"/>
+      <c r="T21" s="13" t="inlineStr"/>
+      <c r="U21" s="14" t="inlineStr"/>
+      <c r="V21" s="14" t="inlineStr"/>
+      <c r="W21" s="14" t="inlineStr"/>
+      <c r="X21" s="14" t="inlineStr"/>
+      <c r="Y21" s="14" t="inlineStr"/>
+      <c r="Z21" s="14" t="inlineStr"/>
+      <c r="AA21" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB21" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC21" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD21" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG21" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH21" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI21" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ21" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK21" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL21" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AM21" s="17" t="inlineStr"/>
+      <c r="AN21" s="17" t="inlineStr"/>
+      <c r="AO21" s="17" t="inlineStr"/>
+      <c r="AP21" s="17" t="inlineStr"/>
+      <c r="AQ21" s="17" t="inlineStr"/>
+      <c r="AR21" s="17" t="inlineStr"/>
+      <c r="AS21" s="18" t="inlineStr"/>
+      <c r="AT21" s="18" t="inlineStr"/>
+      <c r="AU21" s="18" t="inlineStr"/>
+      <c r="AV21" s="18" t="inlineStr"/>
+      <c r="AW21" s="18" t="inlineStr"/>
+      <c r="AX21" s="18" t="inlineStr"/>
+      <c r="AY21" s="19" t="inlineStr"/>
+      <c r="AZ21" s="19" t="inlineStr"/>
+      <c r="BA21" s="19" t="inlineStr"/>
+      <c r="BB21" s="19" t="inlineStr"/>
+      <c r="BC21" s="19" t="inlineStr"/>
+      <c r="BD21" s="19" t="inlineStr"/>
+      <c r="BE21" s="19" t="inlineStr"/>
+      <c r="BF21" s="20" t="inlineStr"/>
+      <c r="BG21" s="20" t="inlineStr"/>
+      <c r="BH21" s="20" t="inlineStr"/>
+      <c r="BI21" s="20" t="inlineStr"/>
+      <c r="BJ21" s="20" t="inlineStr"/>
+      <c r="BK21" s="20" t="inlineStr"/>
+      <c r="BL21" s="20" t="inlineStr"/>
+      <c r="BM21" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C015</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>André Camargo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Consultor Externo</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>100001</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PROD100002</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Produto de Teste - Processo 100002</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>50</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N22" s="12" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="O22" s="13" t="inlineStr"/>
+      <c r="P22" s="13" t="inlineStr"/>
+      <c r="Q22" s="13" t="inlineStr"/>
+      <c r="R22" s="13" t="inlineStr"/>
+      <c r="S22" s="13" t="inlineStr"/>
+      <c r="T22" s="13" t="inlineStr"/>
+      <c r="U22" s="14" t="inlineStr"/>
+      <c r="V22" s="14" t="inlineStr"/>
+      <c r="W22" s="14" t="inlineStr"/>
+      <c r="X22" s="14" t="inlineStr"/>
+      <c r="Y22" s="14" t="inlineStr"/>
+      <c r="Z22" s="14" t="inlineStr"/>
+      <c r="AA22" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB22" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC22" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD22" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG22" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH22" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI22" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ22" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK22" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL22" s="16" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AM22" s="17" t="inlineStr"/>
+      <c r="AN22" s="17" t="inlineStr"/>
+      <c r="AO22" s="17" t="inlineStr"/>
+      <c r="AP22" s="17" t="inlineStr"/>
+      <c r="AQ22" s="17" t="inlineStr"/>
+      <c r="AR22" s="17" t="inlineStr"/>
+      <c r="AS22" s="18" t="inlineStr"/>
+      <c r="AT22" s="18" t="inlineStr"/>
+      <c r="AU22" s="18" t="inlineStr"/>
+      <c r="AV22" s="18" t="inlineStr"/>
+      <c r="AW22" s="18" t="inlineStr"/>
+      <c r="AX22" s="18" t="inlineStr"/>
+      <c r="AY22" s="19" t="inlineStr"/>
+      <c r="AZ22" s="19" t="inlineStr"/>
+      <c r="BA22" s="19" t="inlineStr"/>
+      <c r="BB22" s="19" t="inlineStr"/>
+      <c r="BC22" s="19" t="inlineStr"/>
+      <c r="BD22" s="19" t="inlineStr"/>
+      <c r="BE22" s="19" t="inlineStr"/>
+      <c r="BF22" s="20" t="inlineStr"/>
+      <c r="BG22" s="20" t="inlineStr"/>
+      <c r="BH22" s="20" t="inlineStr"/>
+      <c r="BI22" s="20" t="inlineStr"/>
+      <c r="BJ22" s="20" t="inlineStr"/>
+      <c r="BK22" s="20" t="inlineStr"/>
+      <c r="BL22" s="20" t="inlineStr"/>
+      <c r="BM22" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0.255</v>
       </c>
     </row>
   </sheetData>
@@ -3233,7 +3983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3264,47 +4014,218 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>SALDO_A_RECEBER</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL_COMISSAO_ANTECIPACOES</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL_COMISSAO_REGULARES</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL_COMISSAO_ACUMULADA</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS_PROCESSO</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS_PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS_CALCULO_MEDIAS</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MES_ANO_FATURAMENTO</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TCMP_JSON</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>FCMP_JSON</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TCMP_DETALHES_JSON</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>FCMP_DETALHES_JSON</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>COLABORADORES_ENVOLVIDOS</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>DATA_PRIMEIRO_PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>DATA_ULTIMO_PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>QUANTIDADE_PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ULTIMA_ATUALIZACAO</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>COMISSOES_ADIANTADAS_JSON</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS_RECONCILIACAO</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OBSERVACOES</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>TOTAL_ADIANTADO_COMISSAO</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>STATUS_PAGAMENTO</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>STATUS_RECONCILIACAO</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>STATUS_PROCESSO_ANALISE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>STATUS_CALCULO_MEDIAS</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>MES_ANO_FATURAMENTO</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>TCMP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>FCMP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ULTIMA_ATUALIZACAO</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100001</v>
+      </c>
+      <c r="B2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>FATURADO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CALCULADO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>{"Alessandro Cappi": 0.010000000000000002}</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{"Alessandro Cappi": 1.0}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 50.0, "soma_ponderada": 50.0, "fcmp_final": 1.0}}</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Alessandro Cappi</t>
+        </is>
+      </c>
+      <c r="S2" s="21" t="n">
+        <v>45879</v>
+      </c>
+      <c r="T2" s="21" t="n">
+        <v>45879</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" s="21" t="n">
+        <v>46001.53568858797</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
         </is>
       </c>
     </row>
@@ -3412,7 +4333,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3475</v>
+        <v>0.5615</v>
       </c>
     </row>
     <row r="3">
@@ -3432,7 +4353,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.66</v>
+        <v>1.027</v>
       </c>
     </row>
     <row r="4">
@@ -3512,7 +4433,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.72</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="8">
@@ -3532,7 +4453,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="9">
@@ -3672,7 +4593,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.9625000000000001</v>
+        <v>1.312</v>
       </c>
     </row>
     <row r="16">
@@ -4366,7 +5287,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alessandro Cappi</t>
+          <t>André Caramello</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4376,12 +5297,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PROD100002</t>
+          <t>PROD400001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SSO</t>
+          <t>Hidrologia</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -4389,12 +5310,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ION</t>
+          <t>ISCO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -4443,7 +5364,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>André Caramello</t>
+          <t>Alessandro Cappi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4453,12 +5374,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PROD400001</t>
+          <t>PROD100002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hidrologia</t>
+          <t>SSO</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -4466,12 +5387,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ISCO</t>
+          <t>ION</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -4587,7 +5508,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-12-04T15:08:34.340821</t>
+          <t>2025-12-10T13:05:18.041388</t>
         </is>
       </c>
     </row>
@@ -4666,7 +5587,7 @@
           <t>taxa_rateio_aplicada</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>fator_correcao_fc</t>
         </is>
@@ -4691,152 +5612,152 @@
           <t>cross_selling_decision</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>peso_fat_linha</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>realizado_fat_linha</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>meta_fat_linha</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>ating_fat_linha</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>ating_cap_fat_linha</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>comp_fc_fat_linha</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>peso_conv_linha</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>realizado_conv_linha</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="Z1" s="5" t="inlineStr">
         <is>
           <t>meta_conv_linha</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AA1" s="5" t="inlineStr">
         <is>
           <t>ating_conv_linha</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AB1" s="5" t="inlineStr">
         <is>
           <t>ating_cap_conv_linha</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AC1" s="5" t="inlineStr">
         <is>
           <t>comp_fc_conv_linha</t>
         </is>
       </c>
-      <c r="AD1" s="5" t="inlineStr">
+      <c r="AD1" s="6" t="inlineStr">
         <is>
           <t>peso_fat_ind</t>
         </is>
       </c>
-      <c r="AE1" s="5" t="inlineStr">
+      <c r="AE1" s="6" t="inlineStr">
         <is>
           <t>realizado_fat_ind</t>
         </is>
       </c>
-      <c r="AF1" s="5" t="inlineStr">
+      <c r="AF1" s="6" t="inlineStr">
         <is>
           <t>meta_fat_ind</t>
         </is>
       </c>
-      <c r="AG1" s="5" t="inlineStr">
+      <c r="AG1" s="6" t="inlineStr">
         <is>
           <t>ating_fat_ind</t>
         </is>
       </c>
-      <c r="AH1" s="5" t="inlineStr">
+      <c r="AH1" s="6" t="inlineStr">
         <is>
           <t>ating_cap_fat_ind</t>
         </is>
       </c>
-      <c r="AI1" s="5" t="inlineStr">
+      <c r="AI1" s="6" t="inlineStr">
         <is>
           <t>comp_fc_fat_ind</t>
         </is>
       </c>
-      <c r="AJ1" s="6" t="inlineStr">
+      <c r="AJ1" s="7" t="inlineStr">
         <is>
           <t>peso_conv_ind</t>
         </is>
       </c>
-      <c r="AK1" s="6" t="inlineStr">
+      <c r="AK1" s="7" t="inlineStr">
         <is>
           <t>realizado_conv_ind</t>
         </is>
       </c>
-      <c r="AL1" s="6" t="inlineStr">
+      <c r="AL1" s="7" t="inlineStr">
         <is>
           <t>meta_conv_ind</t>
         </is>
       </c>
-      <c r="AM1" s="6" t="inlineStr">
+      <c r="AM1" s="7" t="inlineStr">
         <is>
           <t>ating_conv_ind</t>
         </is>
       </c>
-      <c r="AN1" s="6" t="inlineStr">
+      <c r="AN1" s="7" t="inlineStr">
         <is>
           <t>ating_cap_conv_ind</t>
         </is>
       </c>
-      <c r="AO1" s="6" t="inlineStr">
+      <c r="AO1" s="7" t="inlineStr">
         <is>
           <t>comp_fc_conv_ind</t>
         </is>
       </c>
-      <c r="AP1" s="9" t="inlineStr">
+      <c r="AP1" s="10" t="inlineStr">
         <is>
           <t>peso_rentab</t>
         </is>
       </c>
-      <c r="AQ1" s="9" t="inlineStr">
+      <c r="AQ1" s="10" t="inlineStr">
         <is>
           <t>realizado_rentab</t>
         </is>
       </c>
-      <c r="AR1" s="9" t="inlineStr">
+      <c r="AR1" s="10" t="inlineStr">
         <is>
           <t>meta_rentab</t>
         </is>
       </c>
-      <c r="AS1" s="9" t="inlineStr">
+      <c r="AS1" s="10" t="inlineStr">
         <is>
           <t>ating_rentab</t>
         </is>
       </c>
-      <c r="AT1" s="9" t="inlineStr">
+      <c r="AT1" s="10" t="inlineStr">
         <is>
           <t>ating_cap_rentab</t>
         </is>
       </c>
-      <c r="AU1" s="9" t="inlineStr">
+      <c r="AU1" s="10" t="inlineStr">
         <is>
           <t>comp_fc_rentab</t>
         </is>
